--- a/Resultados de la votación 2019.xlsx
+++ b/Resultados de la votación 2019.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5fa8a9efe53b17c/Documentos/TP FINAL DATOS/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_252AAE1A57245EB1D6B853B9ECCAFFF85EB24B53" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310"/>
+    <workbookView xWindow="-408" yWindow="648" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="resultados votación 2019" sheetId="1" r:id="rId1"/>
@@ -12,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'resultados votación 2019'!$A$1:$I$214</definedName>
   </definedNames>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -20,6 +26,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -677,11 +689,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_ [$$-2C0A]\ * #,##0.00_ ;_ [$$-2C0A]\ * \-#,##0.00_ ;_ [$$-2C0A]\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_ [$$-2C0A]\ * #,##0.00_ ;_ [$$-2C0A]\ * \-#,##0.00_ ;_ [$$-2C0A]\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -914,30 +926,26 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -952,13 +960,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -967,13 +972,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -991,48 +990,23 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1040,14 +1014,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1061,10 +1044,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1374,34 +1357,34 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M214"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" customWidth="1"/>
-    <col min="2" max="2" width="9.42578125" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="61.140625" style="17" customWidth="1"/>
-    <col min="7" max="7" width="23.5703125" customWidth="1"/>
-    <col min="8" max="8" width="22.28515625" style="16" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.44140625" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" style="7" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="61.109375" style="14" customWidth="1"/>
+    <col min="7" max="7" width="23.5546875" customWidth="1"/>
+    <col min="8" max="8" width="22.33203125" style="13" customWidth="1"/>
+    <col min="9" max="9" width="20.109375" customWidth="1"/>
     <col min="10" max="10" width="21" customWidth="1"/>
     <col min="13" max="13" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="77.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="77.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>199</v>
       </c>
@@ -1426,147 +1409,147 @@
       <c r="H1" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="16" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22">
+    <row r="2" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="17">
         <v>3</v>
       </c>
-      <c r="B2" s="23">
+      <c r="B2" s="18">
         <v>1182</v>
       </c>
-      <c r="C2" s="23">
+      <c r="C2" s="18">
         <v>1</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="21">
         <v>3000000</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="I2" s="27"/>
-    </row>
-    <row r="3" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="28">
+      <c r="I2" s="22"/>
+    </row>
+    <row r="3" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="23">
         <v>7</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="8">
         <v>885</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="8">
         <v>2</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="11">
         <v>810000</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I3" s="29"/>
-    </row>
-    <row r="4" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28">
+      <c r="I3" s="24"/>
+    </row>
+    <row r="4" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="23">
         <v>1</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="8">
         <v>845</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="8">
         <v>3</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="11">
         <v>2500000</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I4" s="29"/>
-    </row>
-    <row r="5" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="28">
+      <c r="I4" s="24"/>
+    </row>
+    <row r="5" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="23">
         <v>4</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="8">
         <v>568</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="8">
         <v>4</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="11">
         <v>3000000</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I5" s="29"/>
-    </row>
-    <row r="6" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28">
+      <c r="I5" s="24"/>
+    </row>
+    <row r="6" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="23">
         <v>5</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="8">
         <v>393</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="8">
         <v>5</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="11">
         <v>680000</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I6" s="29"/>
-    </row>
-    <row r="7" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="30">
+      <c r="I6" s="24"/>
+    </row>
+    <row r="7" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="25">
         <v>12</v>
       </c>
       <c r="B7" s="3">
@@ -1584,16 +1567,16 @@
       <c r="F7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="12">
         <v>1476923</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I7" s="31"/>
-    </row>
-    <row r="8" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="30">
+      <c r="I7" s="24"/>
+    </row>
+    <row r="8" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="25">
         <v>6</v>
       </c>
       <c r="B8" s="3">
@@ -1611,17 +1594,17 @@
       <c r="F8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="12">
         <v>387000</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I8" s="31"/>
-      <c r="M8" s="53"/>
-    </row>
-    <row r="9" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="30">
+      <c r="I8" s="24"/>
+      <c r="M8" s="42"/>
+    </row>
+    <row r="9" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="25">
         <v>11</v>
       </c>
       <c r="B9" s="3">
@@ -1639,16 +1622,16 @@
       <c r="F9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="12">
         <v>1150000</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I9" s="31"/>
-    </row>
-    <row r="10" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="30">
+      <c r="I9" s="24"/>
+    </row>
+    <row r="10" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="25">
         <v>2</v>
       </c>
       <c r="B10" s="3">
@@ -1666,16 +1649,16 @@
       <c r="F10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="12">
         <v>430000</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I10" s="31"/>
-    </row>
-    <row r="11" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="30">
+      <c r="I10" s="24"/>
+    </row>
+    <row r="11" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="25">
         <v>13</v>
       </c>
       <c r="B11" s="3">
@@ -1693,16 +1676,16 @@
       <c r="F11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="12">
         <v>1526644</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I11" s="31"/>
-    </row>
-    <row r="12" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="30">
+      <c r="I11" s="24"/>
+    </row>
+    <row r="12" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="25">
         <v>9</v>
       </c>
       <c r="B12" s="3">
@@ -1720,16 +1703,16 @@
       <c r="F12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="12">
         <v>600000</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I12" s="31"/>
-    </row>
-    <row r="13" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="30">
+      <c r="I12" s="24"/>
+    </row>
+    <row r="13" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="25">
         <v>8</v>
       </c>
       <c r="B13" s="3">
@@ -1747,181 +1730,181 @@
       <c r="F13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="12">
         <v>180000</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I13" s="31"/>
-    </row>
-    <row r="14" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="32">
+      <c r="I13" s="24"/>
+    </row>
+    <row r="14" spans="1:13" s="6" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="26">
         <v>10</v>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="27">
         <v>24</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="27">
         <v>13</v>
       </c>
-      <c r="D14" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="E14" s="34" t="s">
+      <c r="D14" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="E14" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="F14" s="35" t="s">
+      <c r="F14" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="30">
         <v>1119000</v>
       </c>
-      <c r="H14" s="35" t="s">
-        <v>200</v>
-      </c>
-      <c r="I14" s="45">
+      <c r="H14" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="I14" s="36">
         <f>SUM(G2:G6)</f>
         <v>9990000</v>
       </c>
     </row>
-    <row r="15" spans="1:13" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="22">
+    <row r="15" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="17">
         <v>3</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="18">
         <v>2257</v>
       </c>
-      <c r="C15" s="23">
+      <c r="C15" s="18">
         <v>1</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="F15" s="25" t="s">
+      <c r="F15" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="21">
         <v>3000000</v>
       </c>
-      <c r="H15" s="25" t="s">
+      <c r="H15" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="I15" s="37"/>
-    </row>
-    <row r="16" spans="1:13" s="8" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28">
+      <c r="I15" s="31"/>
+    </row>
+    <row r="16" spans="1:13" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="23">
         <v>9</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="8">
         <v>1193</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="8">
         <v>2</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="11">
         <v>3000000</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I16" s="29"/>
-    </row>
-    <row r="17" spans="1:9" s="8" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="28">
+      <c r="I16" s="24"/>
+    </row>
+    <row r="17" spans="1:9" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="23">
         <v>10</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="8">
         <v>979</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="8">
         <v>3</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="11">
         <v>675000</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I17" s="29"/>
-    </row>
-    <row r="18" spans="1:9" s="8" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="28">
+      <c r="I17" s="24"/>
+    </row>
+    <row r="18" spans="1:9" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="23">
         <v>14</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="8">
         <v>767</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="8">
         <v>4</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="11">
         <v>3000000</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I18" s="29"/>
-    </row>
-    <row r="19" spans="1:9" s="8" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="28">
+      <c r="I18" s="24"/>
+    </row>
+    <row r="19" spans="1:9" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="23">
         <v>16</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="8">
         <v>603</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="8">
         <v>5</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="11">
         <v>370000</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="H19" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I19" s="29"/>
-    </row>
-    <row r="20" spans="1:9" s="8" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="30">
+      <c r="I19" s="24"/>
+    </row>
+    <row r="20" spans="1:9" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="25">
         <v>7</v>
       </c>
       <c r="B20" s="3">
@@ -1939,16 +1922,16 @@
       <c r="F20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="12">
         <v>3000000</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I20" s="29"/>
-    </row>
-    <row r="21" spans="1:9" s="8" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="30">
+      <c r="I20" s="24"/>
+    </row>
+    <row r="21" spans="1:9" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="25">
         <v>22</v>
       </c>
       <c r="B21" s="3">
@@ -1966,16 +1949,16 @@
       <c r="F21" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="12">
         <v>3000000</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I21" s="29"/>
-    </row>
-    <row r="22" spans="1:9" s="8" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="30">
+      <c r="I21" s="24"/>
+    </row>
+    <row r="22" spans="1:9" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="25">
         <v>12</v>
       </c>
       <c r="B22" s="3">
@@ -1993,70 +1976,70 @@
       <c r="F22" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G22" s="15">
+      <c r="G22" s="12">
         <v>3000000</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I22" s="29"/>
-    </row>
-    <row r="23" spans="1:9" s="8" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="28">
+      <c r="I22" s="24"/>
+    </row>
+    <row r="23" spans="1:9" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="23">
         <v>17</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="8">
         <v>375</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="8">
         <v>9</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="F23" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="14">
+      <c r="G23" s="11">
         <v>275000</v>
       </c>
-      <c r="H23" s="12" t="s">
+      <c r="H23" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I23" s="29"/>
-    </row>
-    <row r="24" spans="1:9" s="8" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="28">
+      <c r="I23" s="24"/>
+    </row>
+    <row r="24" spans="1:9" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="23">
         <v>6</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="8">
         <v>375</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="8">
         <v>10</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F24" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G24" s="14">
+      <c r="G24" s="11">
         <v>550000</v>
       </c>
-      <c r="H24" s="12" t="s">
+      <c r="H24" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I24" s="29"/>
-    </row>
-    <row r="25" spans="1:9" s="8" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="30">
+      <c r="I24" s="24"/>
+    </row>
+    <row r="25" spans="1:9" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="25">
         <v>15</v>
       </c>
       <c r="B25" s="3">
@@ -2074,43 +2057,43 @@
       <c r="F25" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G25" s="15">
+      <c r="G25" s="12">
         <v>1660000</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I25" s="29"/>
-    </row>
-    <row r="26" spans="1:9" s="8" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="28">
+      <c r="I25" s="24"/>
+    </row>
+    <row r="26" spans="1:9" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="23">
         <v>4</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="8">
         <v>290</v>
       </c>
-      <c r="C26" s="10">
+      <c r="C26" s="8">
         <v>12</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="F26" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G26" s="14">
+      <c r="G26" s="11">
         <v>320000</v>
       </c>
-      <c r="H26" s="12" t="s">
+      <c r="H26" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I26" s="29"/>
-    </row>
-    <row r="27" spans="1:9" s="8" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="30">
+      <c r="I26" s="24"/>
+    </row>
+    <row r="27" spans="1:9" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="25">
         <v>5</v>
       </c>
       <c r="B27" s="3">
@@ -2128,16 +2111,16 @@
       <c r="F27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="12">
         <v>2850000</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I27" s="29"/>
-    </row>
-    <row r="28" spans="1:9" s="8" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30">
+      <c r="I27" s="24"/>
+    </row>
+    <row r="28" spans="1:9" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="25">
         <v>13</v>
       </c>
       <c r="B28" s="3">
@@ -2155,70 +2138,70 @@
       <c r="F28" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G28" s="15">
+      <c r="G28" s="12">
         <v>3000000</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I28" s="29"/>
-    </row>
-    <row r="29" spans="1:9" s="8" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="28">
+      <c r="I28" s="24"/>
+    </row>
+    <row r="29" spans="1:9" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="23">
         <v>11</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="8">
         <v>224</v>
       </c>
-      <c r="C29" s="10">
+      <c r="C29" s="8">
         <v>15</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="F29" s="12" t="s">
+      <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G29" s="14">
+      <c r="G29" s="11">
         <v>483000</v>
       </c>
-      <c r="H29" s="12" t="s">
+      <c r="H29" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I29" s="29"/>
-    </row>
-    <row r="30" spans="1:9" s="8" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="28">
+      <c r="I29" s="24"/>
+    </row>
+    <row r="30" spans="1:9" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="23">
         <v>18</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="8">
         <v>216</v>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="8">
         <v>16</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="F30" s="12" t="s">
+      <c r="F30" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="G30" s="14">
+      <c r="G30" s="11">
         <v>260000</v>
       </c>
-      <c r="H30" s="12" t="s">
+      <c r="H30" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I30" s="29"/>
-    </row>
-    <row r="31" spans="1:9" s="8" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="30">
+      <c r="I30" s="24"/>
+    </row>
+    <row r="31" spans="1:9" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="25">
         <v>2</v>
       </c>
       <c r="B31" s="3">
@@ -2236,16 +2219,16 @@
       <c r="F31" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G31" s="15">
+      <c r="G31" s="12">
         <v>3000000</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I31" s="29"/>
-    </row>
-    <row r="32" spans="1:9" s="8" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="30">
+      <c r="I31" s="24"/>
+    </row>
+    <row r="32" spans="1:9" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="25">
         <v>8</v>
       </c>
       <c r="B32" s="3">
@@ -2263,43 +2246,43 @@
       <c r="F32" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G32" s="15">
+      <c r="G32" s="12">
         <v>2055000</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I32" s="29"/>
-    </row>
-    <row r="33" spans="1:9" s="8" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="28">
+      <c r="I32" s="24"/>
+    </row>
+    <row r="33" spans="1:9" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="23">
         <v>1</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="8">
         <v>192</v>
       </c>
-      <c r="C33" s="10">
+      <c r="C33" s="8">
         <v>19</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E33" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="F33" s="12" t="s">
+      <c r="F33" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="G33" s="14">
+      <c r="G33" s="11">
         <v>175000</v>
       </c>
-      <c r="H33" s="12" t="s">
+      <c r="H33" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I33" s="29"/>
-    </row>
-    <row r="34" spans="1:9" s="8" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="30">
+      <c r="I33" s="24"/>
+    </row>
+    <row r="34" spans="1:9" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="25">
         <v>24</v>
       </c>
       <c r="B34" s="3">
@@ -2317,16 +2300,16 @@
       <c r="F34" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G34" s="15">
+      <c r="G34" s="12">
         <v>1239000</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I34" s="29"/>
-    </row>
-    <row r="35" spans="1:9" s="8" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="30">
+      <c r="I34" s="24"/>
+    </row>
+    <row r="35" spans="1:9" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="25">
         <v>20</v>
       </c>
       <c r="B35" s="3">
@@ -2344,16 +2327,16 @@
       <c r="F35" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G35" s="15">
+      <c r="G35" s="12">
         <v>2392500</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I35" s="29"/>
-    </row>
-    <row r="36" spans="1:9" s="8" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="30">
+      <c r="I35" s="24"/>
+    </row>
+    <row r="36" spans="1:9" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="25">
         <v>23</v>
       </c>
       <c r="B36" s="3">
@@ -2371,16 +2354,16 @@
       <c r="F36" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G36" s="15">
+      <c r="G36" s="12">
         <v>706622</v>
       </c>
       <c r="H36" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I36" s="29"/>
-    </row>
-    <row r="37" spans="1:9" s="8" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="30">
+      <c r="I36" s="24"/>
+    </row>
+    <row r="37" spans="1:9" s="6" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="25">
         <v>19</v>
       </c>
       <c r="B37" s="3">
@@ -2398,154 +2381,154 @@
       <c r="F37" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="15">
+      <c r="G37" s="12">
         <v>3000000</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I37" s="29"/>
-    </row>
-    <row r="38" spans="1:9" s="8" customFormat="1" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="32">
+      <c r="I37" s="24"/>
+    </row>
+    <row r="38" spans="1:9" s="6" customFormat="1" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="26">
         <v>21</v>
       </c>
-      <c r="B38" s="33">
+      <c r="B38" s="27">
         <v>52</v>
       </c>
-      <c r="C38" s="33">
+      <c r="C38" s="27">
         <v>24</v>
       </c>
-      <c r="D38" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="E38" s="34" t="s">
+      <c r="D38" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="E38" s="28" t="s">
         <v>198</v>
       </c>
-      <c r="F38" s="35" t="s">
+      <c r="F38" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="G38" s="36">
+      <c r="G38" s="30">
         <v>43400</v>
       </c>
-      <c r="H38" s="35" t="s">
-        <v>200</v>
-      </c>
-      <c r="I38" s="38">
+      <c r="H38" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="I38" s="32">
         <f>SUM(G33,G30,G29,G26,G24,G23,G15,G16,G17,G18,G19)</f>
         <v>12108000</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="22">
+    <row r="39" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="17">
         <v>9</v>
       </c>
-      <c r="B39" s="23">
+      <c r="B39" s="18">
         <v>1032</v>
       </c>
-      <c r="C39" s="23">
+      <c r="C39" s="18">
         <v>1</v>
       </c>
-      <c r="D39" s="23" t="s">
+      <c r="D39" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="E39" s="24" t="s">
+      <c r="E39" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="F39" s="25" t="s">
+      <c r="F39" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="G39" s="26">
+      <c r="G39" s="21">
         <v>3000000</v>
       </c>
-      <c r="H39" s="25" t="s">
+      <c r="H39" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="I39" s="39"/>
-    </row>
-    <row r="40" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="28">
+      <c r="I39" s="31"/>
+    </row>
+    <row r="40" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="23">
         <v>34</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="8">
         <v>842</v>
       </c>
-      <c r="C40" s="10">
+      <c r="C40" s="8">
         <v>2</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E40" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="F40" s="12" t="s">
+      <c r="F40" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G40" s="14">
+      <c r="G40" s="11">
         <v>3000000</v>
       </c>
-      <c r="H40" s="12" t="s">
+      <c r="H40" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I40" s="40"/>
-    </row>
-    <row r="41" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41" s="28">
+      <c r="I40" s="33"/>
+    </row>
+    <row r="41" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="23">
         <v>1</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="8">
         <v>841</v>
       </c>
-      <c r="C41" s="10">
+      <c r="C41" s="8">
         <v>3</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E41" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="F41" s="12" t="s">
+      <c r="F41" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="G41" s="14">
+      <c r="G41" s="11">
         <v>3000000</v>
       </c>
-      <c r="H41" s="12" t="s">
+      <c r="H41" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I41" s="40"/>
-    </row>
-    <row r="42" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="28">
+      <c r="I41" s="33"/>
+    </row>
+    <row r="42" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="23">
         <v>6</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B42" s="8">
         <v>708</v>
       </c>
-      <c r="C42" s="10">
+      <c r="C42" s="8">
         <v>4</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E42" s="11" t="s">
+      <c r="E42" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="F42" s="12" t="s">
+      <c r="F42" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G42" s="14">
+      <c r="G42" s="11">
         <v>3000000</v>
       </c>
-      <c r="H42" s="12" t="s">
+      <c r="H42" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I42" s="40"/>
-    </row>
-    <row r="43" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="30">
+      <c r="I42" s="33"/>
+    </row>
+    <row r="43" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="25">
         <v>19</v>
       </c>
       <c r="B43" s="3">
@@ -2563,16 +2546,16 @@
       <c r="F43" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G43" s="20">
+      <c r="G43" s="15">
         <v>287000</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I43" s="40"/>
-    </row>
-    <row r="44" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="30">
+      <c r="I43" s="33"/>
+    </row>
+    <row r="44" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="25">
         <v>14</v>
       </c>
       <c r="B44" s="3">
@@ -2590,16 +2573,16 @@
       <c r="F44" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="12">
         <v>1560000</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I44" s="40"/>
-    </row>
-    <row r="45" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="30">
+      <c r="I44" s="33"/>
+    </row>
+    <row r="45" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="25">
         <v>11</v>
       </c>
       <c r="B45" s="3">
@@ -2617,16 +2600,16 @@
       <c r="F45" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="12">
         <v>3000000</v>
       </c>
       <c r="H45" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I45" s="40"/>
-    </row>
-    <row r="46" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="30">
+      <c r="I45" s="33"/>
+    </row>
+    <row r="46" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="25">
         <v>32</v>
       </c>
       <c r="B46" s="3">
@@ -2644,16 +2627,16 @@
       <c r="F46" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G46" s="15">
+      <c r="G46" s="12">
         <v>520000</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I46" s="40"/>
-    </row>
-    <row r="47" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="30">
+      <c r="I46" s="33"/>
+    </row>
+    <row r="47" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="25">
         <v>28</v>
       </c>
       <c r="B47" s="3">
@@ -2671,16 +2654,16 @@
       <c r="F47" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G47" s="15">
+      <c r="G47" s="12">
         <v>3000000</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I47" s="40"/>
-    </row>
-    <row r="48" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" s="30">
+      <c r="I47" s="33"/>
+    </row>
+    <row r="48" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="25">
         <v>16</v>
       </c>
       <c r="B48" s="3">
@@ -2698,16 +2681,16 @@
       <c r="F48" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="G48" s="15">
+      <c r="G48" s="12">
         <v>637000</v>
       </c>
       <c r="H48" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I48" s="40"/>
-    </row>
-    <row r="49" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A49" s="30">
+      <c r="I48" s="33"/>
+    </row>
+    <row r="49" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="25">
         <v>21</v>
       </c>
       <c r="B49" s="3">
@@ -2725,16 +2708,16 @@
       <c r="F49" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G49" s="15">
+      <c r="G49" s="12">
         <v>3000000</v>
       </c>
       <c r="H49" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I49" s="40"/>
-    </row>
-    <row r="50" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="30">
+      <c r="I49" s="33"/>
+    </row>
+    <row r="50" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="25">
         <v>12</v>
       </c>
       <c r="B50" s="3">
@@ -2752,16 +2735,16 @@
       <c r="F50" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G50" s="15">
+      <c r="G50" s="12">
         <v>3000000</v>
       </c>
       <c r="H50" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I50" s="40"/>
-    </row>
-    <row r="51" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A51" s="30">
+      <c r="I50" s="33"/>
+    </row>
+    <row r="51" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="25">
         <v>31</v>
       </c>
       <c r="B51" s="3">
@@ -2779,16 +2762,16 @@
       <c r="F51" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G51" s="15">
+      <c r="G51" s="12">
         <v>3000000</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I51" s="40"/>
-    </row>
-    <row r="52" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="30">
+      <c r="I51" s="33"/>
+    </row>
+    <row r="52" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="25">
         <v>15</v>
       </c>
       <c r="B52" s="3">
@@ -2806,16 +2789,16 @@
       <c r="F52" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G52" s="15">
+      <c r="G52" s="12">
         <v>3000000</v>
       </c>
       <c r="H52" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I52" s="40"/>
-    </row>
-    <row r="53" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="30">
+      <c r="I52" s="33"/>
+    </row>
+    <row r="53" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="25">
         <v>10</v>
       </c>
       <c r="B53" s="3">
@@ -2833,16 +2816,16 @@
       <c r="F53" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G53" s="15">
+      <c r="G53" s="12">
         <v>3000000</v>
       </c>
       <c r="H53" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I53" s="40"/>
-    </row>
-    <row r="54" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="30">
+      <c r="I53" s="33"/>
+    </row>
+    <row r="54" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="25">
         <v>2</v>
       </c>
       <c r="B54" s="3">
@@ -2860,16 +2843,16 @@
       <c r="F54" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="G54" s="15">
+      <c r="G54" s="12">
         <v>1590000</v>
       </c>
       <c r="H54" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I54" s="40"/>
-    </row>
-    <row r="55" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="30">
+      <c r="I54" s="33"/>
+    </row>
+    <row r="55" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="25">
         <v>30</v>
       </c>
       <c r="B55" s="3">
@@ -2887,16 +2870,16 @@
       <c r="F55" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="G55" s="15">
+      <c r="G55" s="12">
         <v>1535000</v>
       </c>
       <c r="H55" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I55" s="40"/>
-    </row>
-    <row r="56" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A56" s="30">
+      <c r="I55" s="33"/>
+    </row>
+    <row r="56" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="25">
         <v>20</v>
       </c>
       <c r="B56" s="3">
@@ -2914,16 +2897,16 @@
       <c r="F56" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="G56" s="15">
+      <c r="G56" s="12">
         <v>486000</v>
       </c>
       <c r="H56" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I56" s="40"/>
-    </row>
-    <row r="57" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A57" s="30">
+      <c r="I56" s="33"/>
+    </row>
+    <row r="57" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="25">
         <v>18</v>
       </c>
       <c r="B57" s="3">
@@ -2941,16 +2924,16 @@
       <c r="F57" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="G57" s="15">
+      <c r="G57" s="12">
         <v>678000</v>
       </c>
       <c r="H57" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I57" s="40"/>
-    </row>
-    <row r="58" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="30">
+      <c r="I57" s="33"/>
+    </row>
+    <row r="58" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="25">
         <v>33</v>
       </c>
       <c r="B58" s="3">
@@ -2968,16 +2951,16 @@
       <c r="F58" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="G58" s="15">
+      <c r="G58" s="12">
         <v>1300000</v>
       </c>
       <c r="H58" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I58" s="40"/>
-    </row>
-    <row r="59" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A59" s="30">
+      <c r="I58" s="33"/>
+    </row>
+    <row r="59" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="25">
         <v>17</v>
       </c>
       <c r="B59" s="3">
@@ -2995,16 +2978,16 @@
       <c r="F59" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G59" s="15">
+      <c r="G59" s="12">
         <v>395000</v>
       </c>
       <c r="H59" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I59" s="40"/>
-    </row>
-    <row r="60" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="30">
+      <c r="I59" s="33"/>
+    </row>
+    <row r="60" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="25">
         <v>24</v>
       </c>
       <c r="B60" s="3">
@@ -3022,16 +3005,16 @@
       <c r="F60" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G60" s="15">
+      <c r="G60" s="12">
         <v>2536050</v>
       </c>
       <c r="H60" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I60" s="40"/>
-    </row>
-    <row r="61" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A61" s="30">
+      <c r="I60" s="33"/>
+    </row>
+    <row r="61" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A61" s="25">
         <v>8</v>
       </c>
       <c r="B61" s="3">
@@ -3049,16 +3032,16 @@
       <c r="F61" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="G61" s="15">
+      <c r="G61" s="12">
         <v>1095000</v>
       </c>
       <c r="H61" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I61" s="40"/>
-    </row>
-    <row r="62" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62" s="30">
+      <c r="I61" s="33"/>
+    </row>
+    <row r="62" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="25">
         <v>4</v>
       </c>
       <c r="B62" s="3">
@@ -3076,16 +3059,16 @@
       <c r="F62" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G62" s="15">
+      <c r="G62" s="12">
         <v>540000</v>
       </c>
       <c r="H62" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I62" s="40"/>
-    </row>
-    <row r="63" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="30">
+      <c r="I62" s="33"/>
+    </row>
+    <row r="63" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="25">
         <v>5</v>
       </c>
       <c r="B63" s="3">
@@ -3103,16 +3086,16 @@
       <c r="F63" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G63" s="15">
+      <c r="G63" s="12">
         <v>1522500</v>
       </c>
       <c r="H63" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I63" s="40"/>
-    </row>
-    <row r="64" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="30">
+      <c r="I63" s="33"/>
+    </row>
+    <row r="64" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="25">
         <v>13</v>
       </c>
       <c r="B64" s="3">
@@ -3130,16 +3113,16 @@
       <c r="F64" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G64" s="15">
+      <c r="G64" s="12">
         <v>200000</v>
       </c>
       <c r="H64" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I64" s="40"/>
-    </row>
-    <row r="65" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A65" s="30">
+      <c r="I64" s="33"/>
+    </row>
+    <row r="65" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A65" s="25">
         <v>26</v>
       </c>
       <c r="B65" s="3">
@@ -3157,16 +3140,16 @@
       <c r="F65" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="G65" s="15">
+      <c r="G65" s="12">
         <v>3000000</v>
       </c>
       <c r="H65" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I65" s="40"/>
-    </row>
-    <row r="66" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="30">
+      <c r="I65" s="33"/>
+    </row>
+    <row r="66" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="25">
         <v>3</v>
       </c>
       <c r="B66" s="3">
@@ -3184,43 +3167,43 @@
       <c r="F66" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G66" s="15">
+      <c r="G66" s="12">
         <v>298000</v>
       </c>
       <c r="H66" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I66" s="40"/>
-    </row>
-    <row r="67" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A67" s="28">
+      <c r="I66" s="33"/>
+    </row>
+    <row r="67" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A67" s="23">
         <v>27</v>
       </c>
-      <c r="B67" s="10">
+      <c r="B67" s="8">
         <v>87</v>
       </c>
-      <c r="C67" s="10">
+      <c r="C67" s="8">
         <v>29</v>
       </c>
-      <c r="D67" s="10" t="s">
+      <c r="D67" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E67" s="11" t="s">
+      <c r="E67" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="F67" s="12" t="s">
+      <c r="F67" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="G67" s="14">
+      <c r="G67" s="11">
         <v>120000</v>
       </c>
-      <c r="H67" s="12" t="s">
+      <c r="H67" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I67" s="40"/>
-    </row>
-    <row r="68" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="30">
+      <c r="I67" s="33"/>
+    </row>
+    <row r="68" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="25">
         <v>22</v>
       </c>
       <c r="B68" s="3">
@@ -3238,16 +3221,16 @@
       <c r="F68" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G68" s="15">
+      <c r="G68" s="12">
         <v>3000000</v>
       </c>
       <c r="H68" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I68" s="40"/>
-    </row>
-    <row r="69" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="30">
+      <c r="I68" s="33"/>
+    </row>
+    <row r="69" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="25">
         <v>29</v>
       </c>
       <c r="B69" s="3">
@@ -3265,16 +3248,16 @@
       <c r="F69" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G69" s="15">
+      <c r="G69" s="12">
         <v>2137856</v>
       </c>
       <c r="H69" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I69" s="40"/>
-    </row>
-    <row r="70" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A70" s="30">
+      <c r="I69" s="33"/>
+    </row>
+    <row r="70" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A70" s="25">
         <v>7</v>
       </c>
       <c r="B70" s="3">
@@ -3292,16 +3275,16 @@
       <c r="F70" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G70" s="15">
+      <c r="G70" s="12">
         <v>389000</v>
       </c>
       <c r="H70" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I70" s="40"/>
-    </row>
-    <row r="71" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A71" s="30">
+      <c r="I70" s="33"/>
+    </row>
+    <row r="71" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A71" s="25">
         <v>23</v>
       </c>
       <c r="B71" s="3">
@@ -3319,1345 +3302,1345 @@
       <c r="F71" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="G71" s="15">
+      <c r="G71" s="12">
         <v>1050000</v>
       </c>
       <c r="H71" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I71" s="40"/>
-    </row>
-    <row r="72" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="32">
+      <c r="I71" s="33"/>
+    </row>
+    <row r="72" spans="1:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="26">
         <v>25</v>
       </c>
-      <c r="B72" s="33">
+      <c r="B72" s="27">
         <v>43</v>
       </c>
-      <c r="C72" s="33">
+      <c r="C72" s="27">
         <v>34</v>
       </c>
-      <c r="D72" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="E72" s="34" t="s">
+      <c r="D72" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="E72" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="F72" s="35" t="s">
+      <c r="F72" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="G72" s="36">
+      <c r="G72" s="30">
         <v>303800</v>
       </c>
-      <c r="H72" s="35" t="s">
-        <v>200</v>
-      </c>
-      <c r="I72" s="38">
+      <c r="H72" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="I72" s="32">
         <f>SUM(G67,G42,G41,G40,G39)</f>
         <v>12120000</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="22">
+    <row r="73" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="17">
         <v>3</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B73" s="18">
         <v>2223</v>
       </c>
-      <c r="C73" s="23">
+      <c r="C73" s="18">
         <v>1</v>
       </c>
-      <c r="D73" s="23" t="s">
+      <c r="D73" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="E73" s="24" t="s">
+      <c r="E73" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="F73" s="25" t="s">
+      <c r="F73" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="G73" s="26">
+      <c r="G73" s="21">
         <v>3000000</v>
       </c>
-      <c r="H73" s="25" t="s">
+      <c r="H73" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="I73" s="39"/>
-    </row>
-    <row r="74" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="28">
+      <c r="I73" s="31"/>
+    </row>
+    <row r="74" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="23">
         <v>39</v>
       </c>
-      <c r="B74" s="10">
+      <c r="B74" s="8">
         <v>1376</v>
       </c>
-      <c r="C74" s="10">
+      <c r="C74" s="8">
         <v>2</v>
       </c>
-      <c r="D74" s="10" t="s">
+      <c r="D74" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E74" s="11" t="s">
+      <c r="E74" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="F74" s="12" t="s">
+      <c r="F74" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="G74" s="14">
+      <c r="G74" s="11">
         <v>3000000</v>
       </c>
-      <c r="H74" s="12" t="s">
+      <c r="H74" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I74" s="40"/>
-    </row>
-    <row r="75" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="28">
+      <c r="I74" s="33"/>
+    </row>
+    <row r="75" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="23">
         <v>24</v>
       </c>
-      <c r="B75" s="10">
+      <c r="B75" s="8">
         <v>1233</v>
       </c>
-      <c r="C75" s="10">
+      <c r="C75" s="8">
         <v>3</v>
       </c>
-      <c r="D75" s="10" t="s">
+      <c r="D75" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E75" s="11" t="s">
+      <c r="E75" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="F75" s="12" t="s">
+      <c r="F75" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="G75" s="14">
+      <c r="G75" s="11">
         <v>3000000</v>
       </c>
-      <c r="H75" s="12" t="s">
+      <c r="H75" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I75" s="40"/>
-    </row>
-    <row r="76" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="28">
+      <c r="I75" s="33"/>
+    </row>
+    <row r="76" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="23">
         <v>37</v>
       </c>
-      <c r="B76" s="10">
+      <c r="B76" s="8">
         <v>1057</v>
       </c>
-      <c r="C76" s="10">
+      <c r="C76" s="8">
         <v>4</v>
       </c>
-      <c r="D76" s="10" t="s">
+      <c r="D76" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E76" s="11" t="s">
+      <c r="E76" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="F76" s="12" t="s">
+      <c r="F76" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G76" s="14">
+      <c r="G76" s="11">
         <v>3000000</v>
       </c>
-      <c r="H76" s="12" t="s">
+      <c r="H76" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I76" s="40"/>
-    </row>
-    <row r="77" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A77" s="30">
+      <c r="I76" s="33"/>
+    </row>
+    <row r="77" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A77" s="25">
         <v>14</v>
       </c>
       <c r="B77" s="3">
         <v>982</v>
       </c>
-      <c r="C77" s="18">
+      <c r="C77" s="3">
         <v>5</v>
       </c>
-      <c r="D77" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E77" s="13" t="s">
+      <c r="D77" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E77" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G77" s="20">
+      <c r="G77" s="15">
         <v>3000000</v>
       </c>
       <c r="H77" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I77" s="40"/>
-    </row>
-    <row r="78" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="28">
+      <c r="I77" s="33"/>
+    </row>
+    <row r="78" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="23">
         <v>26</v>
       </c>
-      <c r="B78" s="10">
+      <c r="B78" s="8">
         <v>937</v>
       </c>
-      <c r="C78" s="10">
+      <c r="C78" s="8">
         <v>6</v>
       </c>
-      <c r="D78" s="10" t="s">
+      <c r="D78" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E78" s="11" t="s">
+      <c r="E78" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="F78" s="12" t="s">
+      <c r="F78" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="G78" s="14">
+      <c r="G78" s="11">
         <v>531000</v>
       </c>
-      <c r="H78" s="12" t="s">
+      <c r="H78" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I78" s="40"/>
-    </row>
-    <row r="79" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="30">
+      <c r="I78" s="33"/>
+    </row>
+    <row r="79" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="25">
         <v>18</v>
       </c>
       <c r="B79" s="3">
         <v>885</v>
       </c>
-      <c r="C79" s="18">
+      <c r="C79" s="3">
         <v>7</v>
       </c>
-      <c r="D79" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E79" s="13" t="s">
+      <c r="D79" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E79" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="G79" s="20">
+      <c r="G79" s="15">
         <v>3000000</v>
       </c>
       <c r="H79" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I79" s="40"/>
-    </row>
-    <row r="80" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="28">
+      <c r="I79" s="33"/>
+    </row>
+    <row r="80" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="23">
         <v>15</v>
       </c>
-      <c r="B80" s="10">
+      <c r="B80" s="8">
         <v>867</v>
       </c>
-      <c r="C80" s="10">
+      <c r="C80" s="8">
         <v>8</v>
       </c>
-      <c r="D80" s="10" t="s">
+      <c r="D80" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E80" s="11" t="s">
+      <c r="E80" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="F80" s="12" t="s">
+      <c r="F80" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="G80" s="14">
+      <c r="G80" s="11">
         <v>1000000</v>
       </c>
-      <c r="H80" s="12" t="s">
+      <c r="H80" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I80" s="40"/>
-    </row>
-    <row r="81" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A81" s="30">
+      <c r="I80" s="33"/>
+    </row>
+    <row r="81" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A81" s="25">
         <v>19</v>
       </c>
       <c r="B81" s="3">
         <v>853</v>
       </c>
-      <c r="C81" s="18">
+      <c r="C81" s="3">
         <v>9</v>
       </c>
-      <c r="D81" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E81" s="13" t="s">
+      <c r="D81" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E81" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F81" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="G81" s="15">
+      <c r="G81" s="12">
         <v>3000000</v>
       </c>
       <c r="H81" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I81" s="40"/>
-    </row>
-    <row r="82" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A82" s="30">
+      <c r="I81" s="33"/>
+    </row>
+    <row r="82" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A82" s="25">
         <v>17</v>
       </c>
       <c r="B82" s="3">
         <v>814</v>
       </c>
-      <c r="C82" s="18">
+      <c r="C82" s="3">
         <v>10</v>
       </c>
-      <c r="D82" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E82" s="13" t="s">
+      <c r="D82" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E82" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="G82" s="15">
+      <c r="G82" s="12">
         <v>3000000</v>
       </c>
       <c r="H82" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I82" s="40"/>
-    </row>
-    <row r="83" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A83" s="30">
+      <c r="I82" s="33"/>
+    </row>
+    <row r="83" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A83" s="25">
         <v>16</v>
       </c>
       <c r="B83" s="3">
         <v>799</v>
       </c>
-      <c r="C83" s="18">
+      <c r="C83" s="3">
         <v>11</v>
       </c>
-      <c r="D83" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E83" s="13" t="s">
+      <c r="D83" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E83" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="G83" s="15">
+      <c r="G83" s="12">
         <v>3000000</v>
       </c>
       <c r="H83" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I83" s="40"/>
-    </row>
-    <row r="84" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A84" s="28">
+      <c r="I83" s="33"/>
+    </row>
+    <row r="84" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A84" s="23">
         <v>1</v>
       </c>
-      <c r="B84" s="10">
+      <c r="B84" s="8">
         <v>723</v>
       </c>
-      <c r="C84" s="10">
+      <c r="C84" s="8">
         <v>12</v>
       </c>
-      <c r="D84" s="10" t="s">
+      <c r="D84" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E84" s="11" t="s">
+      <c r="E84" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="F84" s="12" t="s">
+      <c r="F84" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="G84" s="14">
+      <c r="G84" s="11">
         <v>685000</v>
       </c>
-      <c r="H84" s="12" t="s">
+      <c r="H84" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I84" s="41"/>
-    </row>
-    <row r="85" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A85" s="30">
+      <c r="I84" s="34"/>
+    </row>
+    <row r="85" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A85" s="25">
         <v>28</v>
       </c>
       <c r="B85" s="3">
         <v>717</v>
       </c>
-      <c r="C85" s="18">
+      <c r="C85" s="3">
         <v>13</v>
       </c>
-      <c r="D85" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E85" s="13" t="s">
+      <c r="D85" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E85" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="G85" s="15">
+      <c r="G85" s="12">
         <v>3000000</v>
       </c>
       <c r="H85" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I85" s="40"/>
-    </row>
-    <row r="86" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="30">
+      <c r="I85" s="33"/>
+    </row>
+    <row r="86" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="25">
         <v>5</v>
       </c>
       <c r="B86" s="3">
         <v>611</v>
       </c>
-      <c r="C86" s="18">
+      <c r="C86" s="3">
         <v>14</v>
       </c>
-      <c r="D86" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E86" s="13" t="s">
+      <c r="D86" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E86" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="G86" s="15">
+      <c r="G86" s="12">
         <v>3000000</v>
       </c>
       <c r="H86" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I86" s="40"/>
-    </row>
-    <row r="87" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="30">
+      <c r="I86" s="33"/>
+    </row>
+    <row r="87" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="25">
         <v>27</v>
       </c>
       <c r="B87" s="3">
         <v>592</v>
       </c>
-      <c r="C87" s="18">
+      <c r="C87" s="3">
         <v>15</v>
       </c>
-      <c r="D87" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E87" s="13" t="s">
+      <c r="D87" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E87" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="G87" s="15">
+      <c r="G87" s="12">
         <v>2600000</v>
       </c>
       <c r="H87" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I87" s="40"/>
-    </row>
-    <row r="88" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="30">
+      <c r="I87" s="33"/>
+    </row>
+    <row r="88" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="25">
         <v>23</v>
       </c>
       <c r="B88" s="3">
         <v>537</v>
       </c>
-      <c r="C88" s="18">
+      <c r="C88" s="3">
         <v>16</v>
       </c>
-      <c r="D88" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E88" s="13" t="s">
+      <c r="D88" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E88" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G88" s="15">
+      <c r="G88" s="12">
         <v>1495000</v>
       </c>
       <c r="H88" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I88" s="40"/>
-    </row>
-    <row r="89" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="30">
+      <c r="I88" s="33"/>
+    </row>
+    <row r="89" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="25">
         <v>21</v>
       </c>
       <c r="B89" s="3">
         <v>507</v>
       </c>
-      <c r="C89" s="18">
+      <c r="C89" s="3">
         <v>17</v>
       </c>
-      <c r="D89" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E89" s="13" t="s">
+      <c r="D89" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E89" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="G89" s="15">
+      <c r="G89" s="12">
         <v>400000</v>
       </c>
       <c r="H89" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I89" s="40"/>
-    </row>
-    <row r="90" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="30">
+      <c r="I89" s="33"/>
+    </row>
+    <row r="90" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="25">
         <v>11</v>
       </c>
       <c r="B90" s="3">
         <v>493</v>
       </c>
-      <c r="C90" s="18">
+      <c r="C90" s="3">
         <v>18</v>
       </c>
-      <c r="D90" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E90" s="13" t="s">
+      <c r="D90" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E90" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="G90" s="15">
+      <c r="G90" s="12">
         <v>315000</v>
       </c>
       <c r="H90" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I90" s="40"/>
-    </row>
-    <row r="91" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="30">
+      <c r="I90" s="33"/>
+    </row>
+    <row r="91" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="25">
         <v>20</v>
       </c>
       <c r="B91" s="3">
         <v>481</v>
       </c>
-      <c r="C91" s="18">
+      <c r="C91" s="3">
         <v>19</v>
       </c>
-      <c r="D91" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E91" s="13" t="s">
+      <c r="D91" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E91" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="G91" s="15">
+      <c r="G91" s="12">
         <v>2580000</v>
       </c>
       <c r="H91" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I91" s="40"/>
-    </row>
-    <row r="92" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="30">
+      <c r="I91" s="33"/>
+    </row>
+    <row r="92" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="25">
         <v>6</v>
       </c>
       <c r="B92" s="3">
         <v>454</v>
       </c>
-      <c r="C92" s="18">
+      <c r="C92" s="3">
         <v>20</v>
       </c>
-      <c r="D92" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E92" s="13" t="s">
+      <c r="D92" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E92" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="G92" s="15">
+      <c r="G92" s="12">
         <v>2000000</v>
       </c>
       <c r="H92" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I92" s="40"/>
-    </row>
-    <row r="93" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="30">
+      <c r="I92" s="33"/>
+    </row>
+    <row r="93" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="25">
         <v>13</v>
       </c>
       <c r="B93" s="3">
         <v>404</v>
       </c>
-      <c r="C93" s="18">
+      <c r="C93" s="3">
         <v>21</v>
       </c>
-      <c r="D93" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E93" s="13" t="s">
+      <c r="D93" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E93" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="G93" s="15">
+      <c r="G93" s="12">
         <v>2070000</v>
       </c>
       <c r="H93" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I93" s="40"/>
-    </row>
-    <row r="94" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="30">
+      <c r="I93" s="33"/>
+    </row>
+    <row r="94" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="25">
         <v>22</v>
       </c>
       <c r="B94" s="3">
         <v>363</v>
       </c>
-      <c r="C94" s="18">
+      <c r="C94" s="3">
         <v>22</v>
       </c>
-      <c r="D94" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E94" s="13" t="s">
+      <c r="D94" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E94" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F94" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="G94" s="15">
+      <c r="G94" s="12">
         <v>280400</v>
       </c>
       <c r="H94" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I94" s="40"/>
-    </row>
-    <row r="95" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="30">
+      <c r="I94" s="33"/>
+    </row>
+    <row r="95" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="25">
         <v>2</v>
       </c>
       <c r="B95" s="3">
         <v>336</v>
       </c>
-      <c r="C95" s="18">
+      <c r="C95" s="3">
         <v>23</v>
       </c>
-      <c r="D95" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E95" s="13" t="s">
+      <c r="D95" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E95" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F95" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="G95" s="15">
+      <c r="G95" s="12">
         <v>1200000</v>
       </c>
       <c r="H95" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I95" s="40"/>
-    </row>
-    <row r="96" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="30">
+      <c r="I95" s="33"/>
+    </row>
+    <row r="96" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="25">
         <v>35</v>
       </c>
       <c r="B96" s="3">
         <v>332</v>
       </c>
-      <c r="C96" s="18">
+      <c r="C96" s="3">
         <v>24</v>
       </c>
-      <c r="D96" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E96" s="13" t="s">
+      <c r="D96" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E96" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F96" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G96" s="15">
+      <c r="G96" s="12">
         <v>2871000</v>
       </c>
       <c r="H96" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I96" s="40"/>
-    </row>
-    <row r="97" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="30">
+      <c r="I96" s="33"/>
+    </row>
+    <row r="97" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="25">
         <v>30</v>
       </c>
       <c r="B97" s="3">
         <v>321</v>
       </c>
-      <c r="C97" s="18">
+      <c r="C97" s="3">
         <v>25</v>
       </c>
-      <c r="D97" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E97" s="13" t="s">
+      <c r="D97" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E97" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F97" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="G97" s="15">
+      <c r="G97" s="12">
         <v>566000</v>
       </c>
       <c r="H97" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I97" s="40"/>
-    </row>
-    <row r="98" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="30">
+      <c r="I97" s="33"/>
+    </row>
+    <row r="98" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="25">
         <v>25</v>
       </c>
       <c r="B98" s="3">
         <v>294</v>
       </c>
-      <c r="C98" s="18">
+      <c r="C98" s="3">
         <v>26</v>
       </c>
-      <c r="D98" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E98" s="13" t="s">
+      <c r="D98" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E98" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F98" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G98" s="15">
+      <c r="G98" s="12">
         <v>342000</v>
       </c>
       <c r="H98" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I98" s="40"/>
-    </row>
-    <row r="99" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="30">
+      <c r="I98" s="33"/>
+    </row>
+    <row r="99" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="25">
         <v>4</v>
       </c>
       <c r="B99" s="3">
         <v>292</v>
       </c>
-      <c r="C99" s="18">
+      <c r="C99" s="3">
         <v>27</v>
       </c>
-      <c r="D99" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E99" s="13" t="s">
+      <c r="D99" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E99" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F99" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="G99" s="15">
+      <c r="G99" s="12">
         <v>907000</v>
       </c>
       <c r="H99" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I99" s="40"/>
-    </row>
-    <row r="100" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="30">
+      <c r="I99" s="33"/>
+    </row>
+    <row r="100" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="25">
         <v>12</v>
       </c>
       <c r="B100" s="3">
         <v>270</v>
       </c>
-      <c r="C100" s="18">
+      <c r="C100" s="3">
         <v>28</v>
       </c>
-      <c r="D100" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E100" s="13" t="s">
+      <c r="D100" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E100" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F100" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G100" s="15">
+      <c r="G100" s="12">
         <v>2283750</v>
       </c>
       <c r="H100" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I100" s="40"/>
-    </row>
-    <row r="101" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="30">
+      <c r="I100" s="33"/>
+    </row>
+    <row r="101" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="25">
         <v>40</v>
       </c>
       <c r="B101" s="3">
         <v>259</v>
       </c>
-      <c r="C101" s="18">
+      <c r="C101" s="3">
         <v>29</v>
       </c>
-      <c r="D101" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E101" s="13" t="s">
+      <c r="D101" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E101" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F101" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="G101" s="15">
+      <c r="G101" s="12">
         <v>350000</v>
       </c>
       <c r="H101" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I101" s="40"/>
-    </row>
-    <row r="102" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A102" s="30">
+      <c r="I101" s="33"/>
+    </row>
+    <row r="102" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A102" s="25">
         <v>9</v>
       </c>
       <c r="B102" s="3">
         <v>240</v>
       </c>
-      <c r="C102" s="18">
+      <c r="C102" s="3">
         <v>30</v>
       </c>
-      <c r="D102" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E102" s="13" t="s">
+      <c r="D102" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E102" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F102" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="G102" s="15">
+      <c r="G102" s="12">
         <v>2445000</v>
       </c>
       <c r="H102" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I102" s="40"/>
-    </row>
-    <row r="103" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A103" s="30">
+      <c r="I102" s="33"/>
+    </row>
+    <row r="103" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A103" s="25">
         <v>8</v>
       </c>
       <c r="B103" s="3">
         <v>229</v>
       </c>
-      <c r="C103" s="18">
+      <c r="C103" s="3">
         <v>31</v>
       </c>
-      <c r="D103" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E103" s="13" t="s">
+      <c r="D103" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E103" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F103" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="G103" s="15">
+      <c r="G103" s="12">
         <v>495000</v>
       </c>
       <c r="H103" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I103" s="40"/>
-    </row>
-    <row r="104" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A104" s="30">
+      <c r="I103" s="33"/>
+    </row>
+    <row r="104" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A104" s="25">
         <v>41</v>
       </c>
       <c r="B104" s="3">
         <v>217</v>
       </c>
-      <c r="C104" s="18">
+      <c r="C104" s="3">
         <v>32</v>
       </c>
-      <c r="D104" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E104" s="13" t="s">
+      <c r="D104" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E104" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F104" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="G104" s="15">
+      <c r="G104" s="12">
         <v>337400</v>
       </c>
       <c r="H104" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I104" s="40"/>
-    </row>
-    <row r="105" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A105" s="30">
+      <c r="I104" s="33"/>
+    </row>
+    <row r="105" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A105" s="25">
         <v>38</v>
       </c>
       <c r="B105" s="3">
         <v>192</v>
       </c>
-      <c r="C105" s="18">
+      <c r="C105" s="3">
         <v>33</v>
       </c>
-      <c r="D105" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E105" s="13" t="s">
+      <c r="D105" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E105" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F105" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="G105" s="15">
+      <c r="G105" s="12">
         <v>2872744</v>
       </c>
       <c r="H105" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I105" s="40"/>
-    </row>
-    <row r="106" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A106" s="30">
+      <c r="I105" s="33"/>
+    </row>
+    <row r="106" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A106" s="25">
         <v>29</v>
       </c>
       <c r="B106" s="3">
         <v>165</v>
       </c>
-      <c r="C106" s="18">
+      <c r="C106" s="3">
         <v>34</v>
       </c>
-      <c r="D106" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E106" s="13" t="s">
+      <c r="D106" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E106" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F106" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="G106" s="15">
+      <c r="G106" s="12">
         <v>1950000</v>
       </c>
       <c r="H106" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I106" s="40"/>
-    </row>
-    <row r="107" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A107" s="30">
+      <c r="I106" s="33"/>
+    </row>
+    <row r="107" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A107" s="25">
         <v>7</v>
       </c>
       <c r="B107" s="3">
         <v>159</v>
       </c>
-      <c r="C107" s="18">
+      <c r="C107" s="3">
         <v>35</v>
       </c>
-      <c r="D107" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E107" s="13" t="s">
+      <c r="D107" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E107" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F107" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G107" s="15">
+      <c r="G107" s="12">
         <v>778000</v>
       </c>
       <c r="H107" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I107" s="40"/>
-    </row>
-    <row r="108" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="28">
+      <c r="I107" s="33"/>
+    </row>
+    <row r="108" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="23">
         <v>31</v>
       </c>
-      <c r="B108" s="10">
+      <c r="B108" s="8">
         <v>141</v>
       </c>
-      <c r="C108" s="10">
+      <c r="C108" s="8">
         <v>36</v>
       </c>
-      <c r="D108" s="10" t="s">
+      <c r="D108" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E108" s="11" t="s">
+      <c r="E108" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="F108" s="12" t="s">
+      <c r="F108" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G108" s="14">
+      <c r="G108" s="11">
         <v>180000</v>
       </c>
-      <c r="H108" s="12" t="s">
+      <c r="H108" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I108" s="42"/>
-    </row>
-    <row r="109" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="30">
+      <c r="I108" s="35"/>
+    </row>
+    <row r="109" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="25">
         <v>33</v>
       </c>
       <c r="B109" s="3">
         <v>79</v>
       </c>
-      <c r="C109" s="18">
+      <c r="C109" s="3">
         <v>37</v>
       </c>
-      <c r="D109" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E109" s="13" t="s">
+      <c r="D109" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E109" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F109" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="G109" s="15">
+      <c r="G109" s="12">
         <v>1332141</v>
       </c>
       <c r="H109" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I109" s="40"/>
-    </row>
-    <row r="110" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A110" s="30">
+      <c r="I109" s="33"/>
+    </row>
+    <row r="110" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A110" s="25">
         <v>10</v>
       </c>
       <c r="B110" s="3">
         <v>78</v>
       </c>
-      <c r="C110" s="18">
+      <c r="C110" s="3">
         <v>38</v>
       </c>
-      <c r="D110" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E110" s="13" t="s">
+      <c r="D110" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E110" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F110" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="G110" s="15">
+      <c r="G110" s="12">
         <v>314500</v>
       </c>
       <c r="H110" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I110" s="40"/>
-    </row>
-    <row r="111" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A111" s="30">
+      <c r="I110" s="33"/>
+    </row>
+    <row r="111" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A111" s="25">
         <v>36</v>
       </c>
       <c r="B111" s="3">
         <v>71</v>
       </c>
-      <c r="C111" s="18">
+      <c r="C111" s="3">
         <v>39</v>
       </c>
-      <c r="D111" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E111" s="13" t="s">
+      <c r="D111" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E111" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F111" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G111" s="15">
+      <c r="G111" s="12">
         <v>217000</v>
       </c>
       <c r="H111" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I111" s="40"/>
-    </row>
-    <row r="112" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A112" s="30">
+      <c r="I111" s="33"/>
+    </row>
+    <row r="112" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A112" s="25">
         <v>32</v>
       </c>
       <c r="B112" s="3">
         <v>55</v>
       </c>
-      <c r="C112" s="18">
+      <c r="C112" s="3">
         <v>40</v>
       </c>
-      <c r="D112" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E112" s="13" t="s">
+      <c r="D112" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E112" s="4" t="s">
         <v>202</v>
       </c>
       <c r="F112" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="G112" s="15">
+      <c r="G112" s="12">
         <v>1287000</v>
       </c>
       <c r="H112" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I112" s="40"/>
-    </row>
-    <row r="113" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="32">
+      <c r="I112" s="33"/>
+    </row>
+    <row r="113" spans="1:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="26">
         <v>34</v>
       </c>
-      <c r="B113" s="33">
+      <c r="B113" s="27">
         <v>37</v>
       </c>
-      <c r="C113" s="43">
+      <c r="C113" s="27">
         <v>41</v>
       </c>
-      <c r="D113" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="E113" s="44" t="s">
+      <c r="D113" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="E113" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="F113" s="35" t="s">
+      <c r="F113" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="G113" s="36">
+      <c r="G113" s="30">
         <v>1468513</v>
       </c>
-      <c r="H113" s="35" t="s">
-        <v>200</v>
-      </c>
-      <c r="I113" s="38">
+      <c r="H113" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="I113" s="32">
         <f>SUM(G108,G84,G80,G78,G76,G75,G74,G73)</f>
         <v>14396000</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="22">
+    <row r="114" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="17">
         <v>5</v>
       </c>
-      <c r="B114" s="23">
+      <c r="B114" s="18">
         <v>1529</v>
       </c>
-      <c r="C114" s="23">
+      <c r="C114" s="18">
         <v>1</v>
       </c>
-      <c r="D114" s="23" t="s">
+      <c r="D114" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="E114" s="24" t="s">
+      <c r="E114" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="F114" s="25" t="s">
+      <c r="F114" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="G114" s="26">
+      <c r="G114" s="21">
         <v>3000000</v>
       </c>
-      <c r="H114" s="25" t="s">
+      <c r="H114" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="I114" s="39"/>
-    </row>
-    <row r="115" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="28">
+      <c r="I114" s="31"/>
+    </row>
+    <row r="115" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="23">
         <v>1</v>
       </c>
-      <c r="B115" s="10">
+      <c r="B115" s="8">
         <v>1093</v>
       </c>
-      <c r="C115" s="10">
+      <c r="C115" s="8">
         <v>2</v>
       </c>
-      <c r="D115" s="10" t="s">
+      <c r="D115" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E115" s="11" t="s">
+      <c r="E115" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="F115" s="12" t="s">
+      <c r="F115" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="G115" s="14">
+      <c r="G115" s="11">
         <v>2100000</v>
       </c>
-      <c r="H115" s="12" t="s">
+      <c r="H115" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I115" s="40"/>
-    </row>
-    <row r="116" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="28">
+      <c r="I115" s="33"/>
+    </row>
+    <row r="116" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="23">
         <v>7</v>
       </c>
-      <c r="B116" s="10">
+      <c r="B116" s="8">
         <v>640</v>
       </c>
-      <c r="C116" s="10">
+      <c r="C116" s="8">
         <v>3</v>
       </c>
-      <c r="D116" s="10" t="s">
+      <c r="D116" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E116" s="11" t="s">
+      <c r="E116" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="F116" s="12" t="s">
+      <c r="F116" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="G116" s="14">
+      <c r="G116" s="11">
         <v>2400000</v>
       </c>
-      <c r="H116" s="12" t="s">
+      <c r="H116" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I116" s="40"/>
-    </row>
-    <row r="117" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="28">
+      <c r="I116" s="33"/>
+    </row>
+    <row r="117" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="23">
         <v>3</v>
       </c>
-      <c r="B117" s="10">
+      <c r="B117" s="8">
         <v>489</v>
       </c>
-      <c r="C117" s="10">
+      <c r="C117" s="8">
         <v>4</v>
       </c>
-      <c r="D117" s="10" t="s">
+      <c r="D117" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E117" s="11" t="s">
+      <c r="E117" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="F117" s="12" t="s">
+      <c r="F117" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="G117" s="14">
+      <c r="G117" s="11">
         <v>1400000</v>
       </c>
-      <c r="H117" s="12" t="s">
+      <c r="H117" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I117" s="40"/>
-    </row>
-    <row r="118" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="28">
+      <c r="I117" s="33"/>
+    </row>
+    <row r="118" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="23">
         <v>12</v>
       </c>
-      <c r="B118" s="10">
+      <c r="B118" s="8">
         <v>386</v>
       </c>
-      <c r="C118" s="10">
+      <c r="C118" s="8">
         <v>5</v>
       </c>
-      <c r="D118" s="10" t="s">
+      <c r="D118" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E118" s="11" t="s">
+      <c r="E118" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="F118" s="12" t="s">
+      <c r="F118" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="G118" s="14">
+      <c r="G118" s="11">
         <v>575000</v>
       </c>
-      <c r="H118" s="12" t="s">
+      <c r="H118" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I118" s="40"/>
-    </row>
-    <row r="119" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="28">
+      <c r="I118" s="33"/>
+    </row>
+    <row r="119" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="23">
         <v>16</v>
       </c>
-      <c r="B119" s="10">
+      <c r="B119" s="8">
         <v>383</v>
       </c>
-      <c r="C119" s="10">
+      <c r="C119" s="8">
         <v>6</v>
       </c>
-      <c r="D119" s="10" t="s">
+      <c r="D119" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E119" s="11" t="s">
+      <c r="E119" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="F119" s="12" t="s">
+      <c r="F119" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G119" s="14">
+      <c r="G119" s="11">
         <v>768431</v>
       </c>
-      <c r="H119" s="12" t="s">
+      <c r="H119" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I119" s="40"/>
-    </row>
-    <row r="120" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="28">
+      <c r="I119" s="33"/>
+    </row>
+    <row r="120" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="23">
         <v>9</v>
       </c>
-      <c r="B120" s="10">
+      <c r="B120" s="8">
         <v>279</v>
       </c>
-      <c r="C120" s="10">
+      <c r="C120" s="8">
         <v>7</v>
       </c>
-      <c r="D120" s="10" t="s">
+      <c r="D120" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E120" s="11" t="s">
+      <c r="E120" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="F120" s="12" t="s">
+      <c r="F120" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="G120" s="14">
+      <c r="G120" s="11">
         <v>328000</v>
       </c>
-      <c r="H120" s="12" t="s">
+      <c r="H120" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I120" s="40"/>
-    </row>
-    <row r="121" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="30">
+      <c r="I120" s="33"/>
+    </row>
+    <row r="121" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="25">
         <v>6</v>
       </c>
       <c r="B121" s="3">
@@ -4675,16 +4658,16 @@
       <c r="F121" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="G121" s="15">
+      <c r="G121" s="12">
         <v>3000000</v>
       </c>
       <c r="H121" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I121" s="40"/>
-    </row>
-    <row r="122" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="30">
+      <c r="I121" s="33"/>
+    </row>
+    <row r="122" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="25">
         <v>14</v>
       </c>
       <c r="B122" s="3">
@@ -4702,43 +4685,43 @@
       <c r="F122" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="G122" s="15">
+      <c r="G122" s="12">
         <v>2775300</v>
       </c>
       <c r="H122" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I122" s="40"/>
-    </row>
-    <row r="123" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="28">
+      <c r="I122" s="33"/>
+    </row>
+    <row r="123" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="23">
         <v>4</v>
       </c>
-      <c r="B123" s="10">
+      <c r="B123" s="8">
         <v>223</v>
       </c>
-      <c r="C123" s="10">
+      <c r="C123" s="8">
         <v>10</v>
       </c>
-      <c r="D123" s="10" t="s">
+      <c r="D123" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E123" s="11" t="s">
+      <c r="E123" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="F123" s="12" t="s">
+      <c r="F123" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="G123" s="14">
+      <c r="G123" s="11">
         <v>1522500</v>
       </c>
-      <c r="H123" s="12" t="s">
+      <c r="H123" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I123" s="40"/>
-    </row>
-    <row r="124" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A124" s="30">
+      <c r="I123" s="33"/>
+    </row>
+    <row r="124" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A124" s="25">
         <v>11</v>
       </c>
       <c r="B124" s="3">
@@ -4756,16 +4739,16 @@
       <c r="F124" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="G124" s="15">
+      <c r="G124" s="12">
         <v>360000</v>
       </c>
       <c r="H124" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I124" s="40"/>
-    </row>
-    <row r="125" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A125" s="30">
+      <c r="I124" s="33"/>
+    </row>
+    <row r="125" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A125" s="25">
         <v>17</v>
       </c>
       <c r="B125" s="3">
@@ -4783,16 +4766,16 @@
       <c r="F125" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="G125" s="15">
+      <c r="G125" s="12">
         <v>394000</v>
       </c>
       <c r="H125" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I125" s="40"/>
-    </row>
-    <row r="126" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="30">
+      <c r="I125" s="33"/>
+    </row>
+    <row r="126" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="25">
         <v>10</v>
       </c>
       <c r="B126" s="3">
@@ -4810,16 +4793,16 @@
       <c r="F126" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G126" s="15">
+      <c r="G126" s="12">
         <v>240000</v>
       </c>
       <c r="H126" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I126" s="40"/>
-    </row>
-    <row r="127" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A127" s="30">
+      <c r="I126" s="33"/>
+    </row>
+    <row r="127" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A127" s="25">
         <v>8</v>
       </c>
       <c r="B127" s="3">
@@ -4837,16 +4820,16 @@
       <c r="F127" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="G127" s="15">
+      <c r="G127" s="12">
         <v>1176000</v>
       </c>
       <c r="H127" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I127" s="40"/>
-    </row>
-    <row r="128" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A128" s="30">
+      <c r="I127" s="33"/>
+    </row>
+    <row r="128" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A128" s="25">
         <v>2</v>
       </c>
       <c r="B128" s="3">
@@ -4864,16 +4847,16 @@
       <c r="F128" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="G128" s="15">
+      <c r="G128" s="12">
         <v>36000</v>
       </c>
       <c r="H128" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I128" s="40"/>
-    </row>
-    <row r="129" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="30">
+      <c r="I128" s="33"/>
+    </row>
+    <row r="129" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="25">
         <v>15</v>
       </c>
       <c r="B129" s="3">
@@ -4891,127 +4874,127 @@
       <c r="F129" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="G129" s="15">
+      <c r="G129" s="12">
         <v>43400</v>
       </c>
       <c r="H129" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I129" s="40"/>
-    </row>
-    <row r="130" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="32">
+      <c r="I129" s="33"/>
+    </row>
+    <row r="130" spans="1:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A130" s="26">
         <v>13</v>
       </c>
-      <c r="B130" s="33">
+      <c r="B130" s="27">
         <v>39</v>
       </c>
-      <c r="C130" s="33">
+      <c r="C130" s="27">
         <v>17</v>
       </c>
-      <c r="D130" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="E130" s="34" t="s">
+      <c r="D130" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="E130" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="F130" s="35" t="s">
+      <c r="F130" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="G130" s="36">
+      <c r="G130" s="30">
         <v>3000000</v>
       </c>
-      <c r="H130" s="35" t="s">
-        <v>200</v>
-      </c>
-      <c r="I130" s="38">
+      <c r="H130" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="I130" s="32">
         <f>SUM(G123,G120,G119,G118,G117,G116,G115,G114)</f>
         <v>12093931</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="22">
+    <row r="131" spans="1:9" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="17">
         <v>1</v>
       </c>
-      <c r="B131" s="23">
+      <c r="B131" s="18">
         <v>1874</v>
       </c>
-      <c r="C131" s="23">
+      <c r="C131" s="18">
         <v>1</v>
       </c>
-      <c r="D131" s="23" t="s">
+      <c r="D131" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="E131" s="24" t="s">
+      <c r="E131" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="F131" s="25" t="s">
+      <c r="F131" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="G131" s="26">
+      <c r="G131" s="21">
         <v>3000000</v>
       </c>
-      <c r="H131" s="25" t="s">
+      <c r="H131" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="I131" s="39"/>
-    </row>
-    <row r="132" spans="1:9" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="28">
+      <c r="I131" s="31"/>
+    </row>
+    <row r="132" spans="1:9" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="23">
         <v>12</v>
       </c>
-      <c r="B132" s="10">
+      <c r="B132" s="8">
         <v>1254</v>
       </c>
-      <c r="C132" s="10">
+      <c r="C132" s="8">
         <v>2</v>
       </c>
-      <c r="D132" s="10" t="s">
+      <c r="D132" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E132" s="11" t="s">
+      <c r="E132" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="F132" s="12" t="s">
+      <c r="F132" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="G132" s="14">
+      <c r="G132" s="11">
         <v>3000000</v>
       </c>
-      <c r="H132" s="12" t="s">
+      <c r="H132" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I132" s="40"/>
-    </row>
-    <row r="133" spans="1:9" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="28">
+      <c r="I132" s="33"/>
+    </row>
+    <row r="133" spans="1:9" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="23">
         <v>9</v>
       </c>
-      <c r="B133" s="10">
+      <c r="B133" s="8">
         <v>757</v>
       </c>
-      <c r="C133" s="10">
+      <c r="C133" s="8">
         <v>3</v>
       </c>
-      <c r="D133" s="10" t="s">
+      <c r="D133" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E133" s="11" t="s">
+      <c r="E133" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="F133" s="12" t="s">
+      <c r="F133" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G133" s="14">
+      <c r="G133" s="11">
         <v>3000000</v>
       </c>
-      <c r="H133" s="12" t="s">
+      <c r="H133" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I133" s="40"/>
-    </row>
-    <row r="134" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="30">
+      <c r="I133" s="33"/>
+    </row>
+    <row r="134" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="25">
         <v>5</v>
       </c>
       <c r="B134" s="3">
@@ -5029,16 +5012,16 @@
       <c r="F134" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="G134" s="15">
+      <c r="G134" s="12">
         <v>2500000</v>
       </c>
       <c r="H134" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I134" s="40"/>
-    </row>
-    <row r="135" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="30">
+      <c r="I134" s="33"/>
+    </row>
+    <row r="135" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="25">
         <v>6</v>
       </c>
       <c r="B135" s="3">
@@ -5056,43 +5039,43 @@
       <c r="F135" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="G135" s="15">
+      <c r="G135" s="12">
         <v>2000000</v>
       </c>
       <c r="H135" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I135" s="40"/>
-    </row>
-    <row r="136" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="28">
+      <c r="I135" s="33"/>
+    </row>
+    <row r="136" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="23">
         <v>4</v>
       </c>
-      <c r="B136" s="10">
+      <c r="B136" s="8">
         <v>356</v>
       </c>
-      <c r="C136" s="10">
+      <c r="C136" s="8">
         <v>6</v>
       </c>
-      <c r="D136" s="10" t="s">
+      <c r="D136" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E136" s="11" t="s">
+      <c r="E136" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="F136" s="12" t="s">
+      <c r="F136" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="G136" s="14">
+      <c r="G136" s="11">
         <v>750000</v>
       </c>
-      <c r="H136" s="12" t="s">
+      <c r="H136" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I136" s="40"/>
-    </row>
-    <row r="137" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="30">
+      <c r="I136" s="33"/>
+    </row>
+    <row r="137" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="25">
         <v>2</v>
       </c>
       <c r="B137" s="3">
@@ -5110,43 +5093,43 @@
       <c r="F137" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="G137" s="15">
+      <c r="G137" s="12">
         <v>487000</v>
       </c>
       <c r="H137" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I137" s="40"/>
-    </row>
-    <row r="138" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="28">
+      <c r="I137" s="33"/>
+    </row>
+    <row r="138" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="23">
         <v>11</v>
       </c>
-      <c r="B138" s="10">
+      <c r="B138" s="8">
         <v>313</v>
       </c>
-      <c r="C138" s="10">
+      <c r="C138" s="8">
         <v>8</v>
       </c>
-      <c r="D138" s="10" t="s">
+      <c r="D138" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E138" s="11" t="s">
+      <c r="E138" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="F138" s="12" t="s">
+      <c r="F138" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="G138" s="14">
+      <c r="G138" s="11">
         <v>198000</v>
       </c>
-      <c r="H138" s="12" t="s">
+      <c r="H138" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I138" s="40"/>
-    </row>
-    <row r="139" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A139" s="30">
+      <c r="I138" s="33"/>
+    </row>
+    <row r="139" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A139" s="25">
         <v>3</v>
       </c>
       <c r="B139" s="3">
@@ -5164,16 +5147,16 @@
       <c r="F139" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="G139" s="15">
+      <c r="G139" s="12">
         <v>245000</v>
       </c>
       <c r="H139" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I139" s="40"/>
-    </row>
-    <row r="140" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A140" s="30">
+      <c r="I139" s="33"/>
+    </row>
+    <row r="140" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A140" s="25">
         <v>10</v>
       </c>
       <c r="B140" s="3">
@@ -5191,16 +5174,16 @@
       <c r="F140" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G140" s="15">
+      <c r="G140" s="12">
         <v>1413244</v>
       </c>
       <c r="H140" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I140" s="40"/>
-    </row>
-    <row r="141" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A141" s="30">
+      <c r="I140" s="33"/>
+    </row>
+    <row r="141" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A141" s="25">
         <v>7</v>
       </c>
       <c r="B141" s="3">
@@ -5218,181 +5201,181 @@
       <c r="F141" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G141" s="15">
+      <c r="G141" s="12">
         <v>3000000</v>
       </c>
       <c r="H141" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I141" s="40"/>
-    </row>
-    <row r="142" spans="1:9" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="32">
+      <c r="I141" s="33"/>
+    </row>
+    <row r="142" spans="1:9" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A142" s="26">
         <v>8</v>
       </c>
-      <c r="B142" s="33">
+      <c r="B142" s="27">
         <v>157</v>
       </c>
-      <c r="C142" s="33">
+      <c r="C142" s="27">
         <v>12</v>
       </c>
-      <c r="D142" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="E142" s="34" t="s">
+      <c r="D142" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="E142" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="F142" s="35" t="s">
+      <c r="F142" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="G142" s="36">
+      <c r="G142" s="30">
         <v>210000</v>
       </c>
-      <c r="H142" s="35" t="s">
-        <v>200</v>
-      </c>
-      <c r="I142" s="45">
+      <c r="H142" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="I142" s="36">
         <f>SUM(G138,G136,G133,G132,G131)</f>
         <v>9948000</v>
       </c>
     </row>
-    <row r="143" spans="1:9" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A143" s="22">
+    <row r="143" spans="1:9" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A143" s="17">
         <v>6</v>
       </c>
-      <c r="B143" s="23">
+      <c r="B143" s="18">
         <v>1409</v>
       </c>
-      <c r="C143" s="23">
+      <c r="C143" s="18">
         <v>1</v>
       </c>
-      <c r="D143" s="23" t="s">
+      <c r="D143" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="E143" s="24" t="s">
+      <c r="E143" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="F143" s="25" t="s">
+      <c r="F143" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="G143" s="26">
+      <c r="G143" s="21">
         <v>3000000</v>
       </c>
-      <c r="H143" s="25" t="s">
+      <c r="H143" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="I143" s="46"/>
-    </row>
-    <row r="144" spans="1:9" s="6" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="28">
+      <c r="I143" s="22"/>
+    </row>
+    <row r="144" spans="1:9" s="6" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="23">
         <v>4</v>
       </c>
-      <c r="B144" s="10">
+      <c r="B144" s="8">
         <v>978</v>
       </c>
-      <c r="C144" s="10">
+      <c r="C144" s="8">
         <v>2</v>
       </c>
-      <c r="D144" s="10" t="s">
+      <c r="D144" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E144" s="11" t="s">
+      <c r="E144" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="F144" s="12" t="s">
+      <c r="F144" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="G144" s="14">
+      <c r="G144" s="11">
         <v>3000000</v>
       </c>
-      <c r="H144" s="12" t="s">
+      <c r="H144" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I144" s="31"/>
-    </row>
-    <row r="145" spans="1:9" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A145" s="28">
+      <c r="I144" s="24"/>
+    </row>
+    <row r="145" spans="1:9" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A145" s="23">
         <v>18</v>
       </c>
-      <c r="B145" s="10">
+      <c r="B145" s="8">
         <v>962</v>
       </c>
-      <c r="C145" s="10">
+      <c r="C145" s="8">
         <v>3</v>
       </c>
-      <c r="D145" s="10" t="s">
+      <c r="D145" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E145" s="11" t="s">
+      <c r="E145" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="F145" s="12" t="s">
+      <c r="F145" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="G145" s="14">
+      <c r="G145" s="11">
         <v>3000000</v>
       </c>
-      <c r="H145" s="12" t="s">
+      <c r="H145" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I145" s="31"/>
-    </row>
-    <row r="146" spans="1:9" s="6" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="28">
+      <c r="I145" s="24"/>
+    </row>
+    <row r="146" spans="1:9" s="6" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="23">
         <v>28</v>
       </c>
-      <c r="B146" s="10">
+      <c r="B146" s="8">
         <v>937</v>
       </c>
-      <c r="C146" s="10">
+      <c r="C146" s="8">
         <v>4</v>
       </c>
-      <c r="D146" s="10" t="s">
+      <c r="D146" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E146" s="11" t="s">
+      <c r="E146" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="F146" s="12" t="s">
+      <c r="F146" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G146" s="14">
+      <c r="G146" s="11">
         <v>3000000</v>
       </c>
-      <c r="H146" s="12" t="s">
+      <c r="H146" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I146" s="31"/>
-    </row>
-    <row r="147" spans="1:9" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A147" s="28">
+      <c r="I146" s="24"/>
+    </row>
+    <row r="147" spans="1:9" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A147" s="23">
         <v>10</v>
       </c>
-      <c r="B147" s="10">
+      <c r="B147" s="8">
         <v>864</v>
       </c>
-      <c r="C147" s="10">
+      <c r="C147" s="8">
         <v>5</v>
       </c>
-      <c r="D147" s="10" t="s">
+      <c r="D147" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E147" s="11" t="s">
+      <c r="E147" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="F147" s="12" t="s">
+      <c r="F147" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="G147" s="14">
+      <c r="G147" s="11">
         <v>1435000</v>
       </c>
-      <c r="H147" s="12" t="s">
+      <c r="H147" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I147" s="31"/>
-    </row>
-    <row r="148" spans="1:9" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A148" s="30">
+      <c r="I147" s="24"/>
+    </row>
+    <row r="148" spans="1:9" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A148" s="25">
         <v>7</v>
       </c>
       <c r="B148" s="3">
@@ -5410,16 +5393,16 @@
       <c r="F148" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="G148" s="15">
+      <c r="G148" s="12">
         <v>3000000</v>
       </c>
-      <c r="H148" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I148" s="31"/>
-    </row>
-    <row r="149" spans="1:9" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A149" s="30">
+      <c r="H148" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I148" s="24"/>
+    </row>
+    <row r="149" spans="1:9" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A149" s="25">
         <v>13</v>
       </c>
       <c r="B149" s="3">
@@ -5437,16 +5420,16 @@
       <c r="F149" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="G149" s="15">
+      <c r="G149" s="12">
         <v>2450000</v>
       </c>
-      <c r="H149" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I149" s="31"/>
-    </row>
-    <row r="150" spans="1:9" s="6" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="30">
+      <c r="H149" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I149" s="24"/>
+    </row>
+    <row r="150" spans="1:9" s="6" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="25">
         <v>2</v>
       </c>
       <c r="B150" s="3">
@@ -5464,43 +5447,43 @@
       <c r="F150" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="G150" s="15">
+      <c r="G150" s="12">
         <v>3000000</v>
       </c>
-      <c r="H150" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I150" s="31"/>
-    </row>
-    <row r="151" spans="1:9" s="6" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="28">
+      <c r="H150" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I150" s="24"/>
+    </row>
+    <row r="151" spans="1:9" s="6" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="23">
         <v>15</v>
       </c>
-      <c r="B151" s="10">
+      <c r="B151" s="8">
         <v>778</v>
       </c>
-      <c r="C151" s="10">
+      <c r="C151" s="8">
         <v>9</v>
       </c>
-      <c r="D151" s="10" t="s">
+      <c r="D151" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E151" s="11" t="s">
+      <c r="E151" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="F151" s="12" t="s">
+      <c r="F151" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="G151" s="14">
+      <c r="G151" s="11">
         <v>371250</v>
       </c>
-      <c r="H151" s="12" t="s">
+      <c r="H151" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I151" s="31"/>
-    </row>
-    <row r="152" spans="1:9" s="6" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="30">
+      <c r="I151" s="24"/>
+    </row>
+    <row r="152" spans="1:9" s="6" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="25">
         <v>20</v>
       </c>
       <c r="B152" s="3">
@@ -5518,16 +5501,16 @@
       <c r="F152" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="G152" s="15">
+      <c r="G152" s="12">
         <v>3000000</v>
       </c>
-      <c r="H152" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I152" s="31"/>
-    </row>
-    <row r="153" spans="1:9" s="6" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="30">
+      <c r="H152" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I152" s="24"/>
+    </row>
+    <row r="153" spans="1:9" s="6" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="25">
         <v>14</v>
       </c>
       <c r="B153" s="3">
@@ -5545,97 +5528,97 @@
       <c r="F153" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="G153" s="15">
+      <c r="G153" s="12">
         <v>1500000</v>
       </c>
-      <c r="H153" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I153" s="31"/>
-    </row>
-    <row r="154" spans="1:9" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A154" s="28">
+      <c r="H153" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I153" s="24"/>
+    </row>
+    <row r="154" spans="1:9" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A154" s="23">
         <v>8</v>
       </c>
-      <c r="B154" s="10">
+      <c r="B154" s="8">
         <v>552</v>
       </c>
-      <c r="C154" s="10">
+      <c r="C154" s="8">
         <v>12</v>
       </c>
-      <c r="D154" s="10" t="s">
+      <c r="D154" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E154" s="11" t="s">
+      <c r="E154" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="F154" s="12" t="s">
+      <c r="F154" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="G154" s="14">
+      <c r="G154" s="11">
         <v>235000</v>
       </c>
-      <c r="H154" s="12" t="s">
+      <c r="H154" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I154" s="31"/>
-    </row>
-    <row r="155" spans="1:9" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A155" s="28">
+      <c r="I154" s="24"/>
+    </row>
+    <row r="155" spans="1:9" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A155" s="23">
         <v>22</v>
       </c>
-      <c r="B155" s="10">
+      <c r="B155" s="8">
         <v>518</v>
       </c>
-      <c r="C155" s="10">
+      <c r="C155" s="8">
         <v>13</v>
       </c>
-      <c r="D155" s="10" t="s">
+      <c r="D155" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E155" s="11" t="s">
+      <c r="E155" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="F155" s="12" t="s">
+      <c r="F155" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="G155" s="14">
+      <c r="G155" s="11">
         <v>137000</v>
       </c>
-      <c r="H155" s="12" t="s">
+      <c r="H155" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I155" s="31"/>
-    </row>
-    <row r="156" spans="1:9" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="28">
+      <c r="I155" s="24"/>
+    </row>
+    <row r="156" spans="1:9" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="23">
         <v>3</v>
       </c>
-      <c r="B156" s="10">
+      <c r="B156" s="8">
         <v>490</v>
       </c>
-      <c r="C156" s="10">
+      <c r="C156" s="8">
         <v>14</v>
       </c>
-      <c r="D156" s="10" t="s">
+      <c r="D156" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E156" s="11" t="s">
+      <c r="E156" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="F156" s="12" t="s">
+      <c r="F156" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="G156" s="14">
+      <c r="G156" s="11">
         <v>195000</v>
       </c>
-      <c r="H156" s="12" t="s">
+      <c r="H156" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I156" s="31"/>
-    </row>
-    <row r="157" spans="1:9" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A157" s="30">
+      <c r="I156" s="24"/>
+    </row>
+    <row r="157" spans="1:9" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A157" s="25">
         <v>16</v>
       </c>
       <c r="B157" s="3">
@@ -5653,16 +5636,16 @@
       <c r="F157" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="G157" s="15">
+      <c r="G157" s="12">
         <v>1560000</v>
       </c>
-      <c r="H157" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I157" s="31"/>
-    </row>
-    <row r="158" spans="1:9" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A158" s="30">
+      <c r="H157" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I157" s="24"/>
+    </row>
+    <row r="158" spans="1:9" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A158" s="25">
         <v>1</v>
       </c>
       <c r="B158" s="3">
@@ -5680,16 +5663,16 @@
       <c r="F158" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="G158" s="15">
+      <c r="G158" s="12">
         <v>1275000</v>
       </c>
-      <c r="H158" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I158" s="31"/>
-    </row>
-    <row r="159" spans="1:9" s="6" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="30">
+      <c r="H158" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I158" s="24"/>
+    </row>
+    <row r="159" spans="1:9" s="6" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="25">
         <v>24</v>
       </c>
       <c r="B159" s="3">
@@ -5707,16 +5690,16 @@
       <c r="F159" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="G159" s="15">
+      <c r="G159" s="12">
         <v>245000</v>
       </c>
-      <c r="H159" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I159" s="31"/>
-    </row>
-    <row r="160" spans="1:9" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A160" s="30">
+      <c r="H159" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I159" s="24"/>
+    </row>
+    <row r="160" spans="1:9" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A160" s="25">
         <v>25</v>
       </c>
       <c r="B160" s="3">
@@ -5734,16 +5717,16 @@
       <c r="F160" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="G160" s="15">
+      <c r="G160" s="12">
         <v>186000</v>
       </c>
-      <c r="H160" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I160" s="31"/>
-    </row>
-    <row r="161" spans="1:9" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A161" s="30">
+      <c r="H160" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I160" s="24"/>
+    </row>
+    <row r="161" spans="1:9" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A161" s="25">
         <v>23</v>
       </c>
       <c r="B161" s="3">
@@ -5761,16 +5744,16 @@
       <c r="F161" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="G161" s="15">
+      <c r="G161" s="12">
         <v>1180000</v>
       </c>
-      <c r="H161" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I161" s="31"/>
-    </row>
-    <row r="162" spans="1:9" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A162" s="30">
+      <c r="H161" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I161" s="24"/>
+    </row>
+    <row r="162" spans="1:9" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A162" s="25">
         <v>21</v>
       </c>
       <c r="B162" s="3">
@@ -5788,16 +5771,16 @@
       <c r="F162" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="G162" s="15">
+      <c r="G162" s="12">
         <v>3000000</v>
       </c>
-      <c r="H162" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I162" s="31"/>
-    </row>
-    <row r="163" spans="1:9" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A163" s="30">
+      <c r="H162" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I162" s="24"/>
+    </row>
+    <row r="163" spans="1:9" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A163" s="25">
         <v>17</v>
       </c>
       <c r="B163" s="3">
@@ -5815,16 +5798,16 @@
       <c r="F163" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G163" s="15">
+      <c r="G163" s="12">
         <v>965000</v>
       </c>
-      <c r="H163" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I163" s="31"/>
-    </row>
-    <row r="164" spans="1:9" s="6" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="30">
+      <c r="H163" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I163" s="24"/>
+    </row>
+    <row r="164" spans="1:9" s="6" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="25">
         <v>9</v>
       </c>
       <c r="B164" s="3">
@@ -5842,16 +5825,16 @@
       <c r="F164" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G164" s="15">
+      <c r="G164" s="12">
         <v>2283750</v>
       </c>
-      <c r="H164" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I164" s="31"/>
-    </row>
-    <row r="165" spans="1:9" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A165" s="30">
+      <c r="H164" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I164" s="24"/>
+    </row>
+    <row r="165" spans="1:9" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A165" s="25">
         <v>11</v>
       </c>
       <c r="B165" s="3">
@@ -5869,16 +5852,16 @@
       <c r="F165" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="G165" s="15">
+      <c r="G165" s="12">
         <v>1300000</v>
       </c>
-      <c r="H165" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I165" s="31"/>
-    </row>
-    <row r="166" spans="1:9" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A166" s="30">
+      <c r="H165" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I165" s="24"/>
+    </row>
+    <row r="166" spans="1:9" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A166" s="25">
         <v>29</v>
       </c>
       <c r="B166" s="3">
@@ -5896,16 +5879,16 @@
       <c r="F166" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G166" s="15">
+      <c r="G166" s="12">
         <v>2341822</v>
       </c>
-      <c r="H166" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I166" s="31"/>
-    </row>
-    <row r="167" spans="1:9" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A167" s="30">
+      <c r="H166" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I166" s="24"/>
+    </row>
+    <row r="167" spans="1:9" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A167" s="25">
         <v>5</v>
       </c>
       <c r="B167" s="3">
@@ -5923,16 +5906,16 @@
       <c r="F167" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="G167" s="15">
+      <c r="G167" s="12">
         <v>1045000</v>
       </c>
-      <c r="H167" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I167" s="31"/>
-    </row>
-    <row r="168" spans="1:9" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A168" s="30">
+      <c r="H167" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I167" s="24"/>
+    </row>
+    <row r="168" spans="1:9" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A168" s="25">
         <v>19</v>
       </c>
       <c r="B168" s="3">
@@ -5950,16 +5933,16 @@
       <c r="F168" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="G168" s="15">
+      <c r="G168" s="12">
         <v>3000000</v>
       </c>
-      <c r="H168" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I168" s="31"/>
-    </row>
-    <row r="169" spans="1:9" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A169" s="30">
+      <c r="H168" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I168" s="24"/>
+    </row>
+    <row r="169" spans="1:9" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A169" s="25">
         <v>26</v>
       </c>
       <c r="B169" s="3">
@@ -5977,16 +5960,16 @@
       <c r="F169" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="G169" s="15">
+      <c r="G169" s="12">
         <v>650000</v>
       </c>
-      <c r="H169" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I169" s="31"/>
-    </row>
-    <row r="170" spans="1:9" s="6" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="30">
+      <c r="H169" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I169" s="24"/>
+    </row>
+    <row r="170" spans="1:9" s="6" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="25">
         <v>27</v>
       </c>
       <c r="B170" s="3">
@@ -6004,16 +5987,16 @@
       <c r="F170" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="G170" s="15">
+      <c r="G170" s="12">
         <v>2268171</v>
       </c>
-      <c r="H170" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I170" s="31"/>
-    </row>
-    <row r="171" spans="1:9" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A171" s="30">
+      <c r="H170" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I170" s="24"/>
+    </row>
+    <row r="171" spans="1:9" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A171" s="25">
         <v>31</v>
       </c>
       <c r="B171" s="3">
@@ -6031,16 +6014,16 @@
       <c r="F171" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="G171" s="15">
+      <c r="G171" s="12">
         <v>355306</v>
       </c>
-      <c r="H171" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I171" s="31"/>
-    </row>
-    <row r="172" spans="1:9" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A172" s="30">
+      <c r="H171" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I171" s="24"/>
+    </row>
+    <row r="172" spans="1:9" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A172" s="25">
         <v>30</v>
       </c>
       <c r="B172" s="3">
@@ -6058,940 +6041,940 @@
       <c r="F172" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="G172" s="15">
+      <c r="G172" s="12">
         <v>420000</v>
       </c>
-      <c r="H172" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I172" s="31"/>
-    </row>
-    <row r="173" spans="1:9" s="6" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="32">
+      <c r="H172" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I172" s="24"/>
+    </row>
+    <row r="173" spans="1:9" s="6" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A173" s="26">
         <v>12</v>
       </c>
-      <c r="B173" s="33">
+      <c r="B173" s="27">
         <v>80</v>
       </c>
-      <c r="C173" s="33">
+      <c r="C173" s="27">
         <v>31</v>
       </c>
-      <c r="D173" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="E173" s="34" t="s">
+      <c r="D173" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="E173" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="F173" s="35" t="s">
+      <c r="F173" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="G173" s="36">
+      <c r="G173" s="30">
         <v>3000000</v>
       </c>
-      <c r="H173" s="47" t="s">
-        <v>200</v>
-      </c>
-      <c r="I173" s="45">
+      <c r="H173" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="I173" s="36">
         <f>SUM(G156,G155,G154,G151,G147,G146,G145,G144,G143)</f>
         <v>14373250</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A174" s="22">
+    <row r="174" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A174" s="17">
         <v>8</v>
       </c>
-      <c r="B174" s="23">
+      <c r="B174" s="18">
         <v>2789</v>
       </c>
-      <c r="C174" s="23">
+      <c r="C174" s="18">
         <v>1</v>
       </c>
-      <c r="D174" s="23" t="s">
+      <c r="D174" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="E174" s="24" t="s">
+      <c r="E174" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="F174" s="25" t="s">
+      <c r="F174" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="G174" s="26">
+      <c r="G174" s="21">
         <v>3000000</v>
       </c>
-      <c r="H174" s="25" t="s">
+      <c r="H174" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="I174" s="39"/>
-    </row>
-    <row r="175" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="28">
+      <c r="I174" s="31"/>
+    </row>
+    <row r="175" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A175" s="23">
         <v>10</v>
       </c>
-      <c r="B175" s="10">
+      <c r="B175" s="8">
         <v>2100</v>
       </c>
-      <c r="C175" s="10">
+      <c r="C175" s="8">
         <v>2</v>
       </c>
-      <c r="D175" s="10" t="s">
+      <c r="D175" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E175" s="11" t="s">
+      <c r="E175" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="F175" s="12" t="s">
+      <c r="F175" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="G175" s="14">
+      <c r="G175" s="11">
         <v>3000000</v>
       </c>
-      <c r="H175" s="12" t="s">
+      <c r="H175" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I175" s="40"/>
-    </row>
-    <row r="176" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A176" s="28">
+      <c r="I175" s="33"/>
+    </row>
+    <row r="176" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A176" s="23">
         <v>7</v>
       </c>
-      <c r="B176" s="10">
+      <c r="B176" s="8">
         <v>2059</v>
       </c>
-      <c r="C176" s="10">
+      <c r="C176" s="8">
         <v>3</v>
       </c>
-      <c r="D176" s="10" t="s">
+      <c r="D176" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E176" s="11" t="s">
+      <c r="E176" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="F176" s="12" t="s">
+      <c r="F176" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="G176" s="14">
+      <c r="G176" s="11">
         <v>3000000</v>
       </c>
-      <c r="H176" s="12" t="s">
+      <c r="H176" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I176" s="40"/>
-    </row>
-    <row r="177" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A177" s="28">
+      <c r="I176" s="33"/>
+    </row>
+    <row r="177" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A177" s="23">
         <v>19</v>
       </c>
-      <c r="B177" s="10">
+      <c r="B177" s="8">
         <v>1370</v>
       </c>
-      <c r="C177" s="10">
+      <c r="C177" s="8">
         <v>4</v>
       </c>
-      <c r="D177" s="10" t="s">
+      <c r="D177" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E177" s="11" t="s">
+      <c r="E177" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="F177" s="12" t="s">
+      <c r="F177" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="G177" s="14">
+      <c r="G177" s="11">
         <v>3000000</v>
       </c>
-      <c r="H177" s="12" t="s">
+      <c r="H177" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I177" s="40"/>
-    </row>
-    <row r="178" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A178" s="28">
+      <c r="I177" s="33"/>
+    </row>
+    <row r="178" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A178" s="23">
         <v>1</v>
       </c>
-      <c r="B178" s="10">
+      <c r="B178" s="8">
         <v>974</v>
       </c>
-      <c r="C178" s="10">
+      <c r="C178" s="8">
         <v>5</v>
       </c>
-      <c r="D178" s="10" t="s">
+      <c r="D178" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E178" s="11" t="s">
+      <c r="E178" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="F178" s="12" t="s">
+      <c r="F178" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="G178" s="14">
+      <c r="G178" s="11">
         <v>1540000</v>
       </c>
-      <c r="H178" s="12" t="s">
+      <c r="H178" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I178" s="40"/>
-    </row>
-    <row r="179" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A179" s="30">
+      <c r="I178" s="33"/>
+    </row>
+    <row r="179" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A179" s="25">
         <v>9</v>
       </c>
       <c r="B179" s="3">
         <v>917</v>
       </c>
-      <c r="C179" s="18">
+      <c r="C179" s="3">
         <v>6</v>
       </c>
-      <c r="D179" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E179" s="13" t="s">
+      <c r="D179" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E179" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F179" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G179" s="15">
+      <c r="G179" s="12">
         <v>3000000</v>
       </c>
-      <c r="H179" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I179" s="40"/>
-    </row>
-    <row r="180" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A180" s="30">
+      <c r="H179" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I179" s="33"/>
+    </row>
+    <row r="180" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A180" s="25">
         <v>12</v>
       </c>
       <c r="B180" s="3">
         <v>900</v>
       </c>
-      <c r="C180" s="18">
+      <c r="C180" s="3">
         <v>7</v>
       </c>
-      <c r="D180" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E180" s="13" t="s">
+      <c r="D180" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E180" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F180" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="G180" s="15">
+      <c r="G180" s="12">
         <v>3000000</v>
       </c>
-      <c r="H180" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I180" s="40"/>
-    </row>
-    <row r="181" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A181" s="30">
+      <c r="H180" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I180" s="33"/>
+    </row>
+    <row r="181" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A181" s="25">
         <v>13</v>
       </c>
       <c r="B181" s="3">
         <v>787</v>
       </c>
-      <c r="C181" s="18">
+      <c r="C181" s="3">
         <v>8</v>
       </c>
-      <c r="D181" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E181" s="13" t="s">
+      <c r="D181" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E181" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F181" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="G181" s="15">
+      <c r="G181" s="12">
         <v>2000000</v>
       </c>
-      <c r="H181" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I181" s="40"/>
-    </row>
-    <row r="182" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="30">
+      <c r="H181" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I181" s="33"/>
+    </row>
+    <row r="182" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="25">
         <v>4</v>
       </c>
       <c r="B182" s="3">
         <v>760</v>
       </c>
-      <c r="C182" s="18">
+      <c r="C182" s="3">
         <v>9</v>
       </c>
-      <c r="D182" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E182" s="13" t="s">
+      <c r="D182" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E182" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F182" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="G182" s="15">
+      <c r="G182" s="12">
         <v>1200000</v>
       </c>
-      <c r="H182" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I182" s="40"/>
-    </row>
-    <row r="183" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A183" s="30">
+      <c r="H182" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I182" s="33"/>
+    </row>
+    <row r="183" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A183" s="25">
         <v>17</v>
       </c>
       <c r="B183" s="3">
         <v>633</v>
       </c>
-      <c r="C183" s="18">
+      <c r="C183" s="3">
         <v>10</v>
       </c>
-      <c r="D183" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E183" s="13" t="s">
+      <c r="D183" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E183" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F183" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="G183" s="15">
+      <c r="G183" s="12">
         <v>3000000</v>
       </c>
-      <c r="H183" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I183" s="40"/>
-    </row>
-    <row r="184" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="30">
+      <c r="H183" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I183" s="33"/>
+    </row>
+    <row r="184" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="25">
         <v>16</v>
       </c>
       <c r="B184" s="3">
         <v>588</v>
       </c>
-      <c r="C184" s="18">
+      <c r="C184" s="3">
         <v>11</v>
       </c>
-      <c r="D184" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E184" s="13" t="s">
+      <c r="D184" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E184" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F184" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="G184" s="15">
+      <c r="G184" s="12">
         <v>3000000</v>
       </c>
-      <c r="H184" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I184" s="40"/>
-    </row>
-    <row r="185" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="28">
+      <c r="H184" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I184" s="33"/>
+    </row>
+    <row r="185" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="23">
         <v>27</v>
       </c>
-      <c r="B185" s="10">
+      <c r="B185" s="8">
         <v>568</v>
       </c>
-      <c r="C185" s="10">
+      <c r="C185" s="8">
         <v>12</v>
       </c>
-      <c r="D185" s="10" t="s">
+      <c r="D185" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E185" s="11" t="s">
+      <c r="E185" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="F185" s="12" t="s">
+      <c r="F185" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G185" s="14">
+      <c r="G185" s="11">
         <v>738461</v>
       </c>
-      <c r="H185" s="12" t="s">
+      <c r="H185" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I185" s="40"/>
-    </row>
-    <row r="186" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="30">
+      <c r="I185" s="33"/>
+    </row>
+    <row r="186" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="25">
         <v>23</v>
       </c>
       <c r="B186" s="3">
         <v>526</v>
       </c>
-      <c r="C186" s="18">
+      <c r="C186" s="3">
         <v>13</v>
       </c>
-      <c r="D186" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E186" s="13" t="s">
+      <c r="D186" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E186" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F186" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G186" s="15">
+      <c r="G186" s="12">
         <v>3000000</v>
       </c>
-      <c r="H186" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I186" s="40"/>
-    </row>
-    <row r="187" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A187" s="30">
+      <c r="H186" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I186" s="33"/>
+    </row>
+    <row r="187" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A187" s="25">
         <v>11</v>
       </c>
       <c r="B187" s="3">
         <v>510</v>
       </c>
-      <c r="C187" s="18">
+      <c r="C187" s="3">
         <v>14</v>
       </c>
-      <c r="D187" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E187" s="13" t="s">
+      <c r="D187" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E187" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F187" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G187" s="15">
+      <c r="G187" s="12">
         <v>450000</v>
       </c>
-      <c r="H187" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I187" s="40"/>
-    </row>
-    <row r="188" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A188" s="30">
+      <c r="H187" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I187" s="33"/>
+    </row>
+    <row r="188" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A188" s="25">
         <v>21</v>
       </c>
       <c r="B188" s="3">
         <v>501</v>
       </c>
-      <c r="C188" s="18">
+      <c r="C188" s="3">
         <v>15</v>
       </c>
-      <c r="D188" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E188" s="13" t="s">
+      <c r="D188" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E188" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F188" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="G188" s="15">
+      <c r="G188" s="12">
         <v>2000000</v>
       </c>
-      <c r="H188" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I188" s="40"/>
-    </row>
-    <row r="189" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A189" s="30">
+      <c r="H188" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I188" s="33"/>
+    </row>
+    <row r="189" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A189" s="25">
         <v>22</v>
       </c>
       <c r="B189" s="3">
         <v>479</v>
       </c>
-      <c r="C189" s="18">
+      <c r="C189" s="3">
         <v>16</v>
       </c>
-      <c r="D189" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E189" s="13" t="s">
+      <c r="D189" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E189" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F189" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="G189" s="15">
+      <c r="G189" s="12">
         <v>838000</v>
       </c>
-      <c r="H189" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I189" s="40"/>
-    </row>
-    <row r="190" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A190" s="30">
+      <c r="H189" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I189" s="33"/>
+    </row>
+    <row r="190" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A190" s="25">
         <v>5</v>
       </c>
       <c r="B190" s="3">
         <v>468</v>
       </c>
-      <c r="C190" s="18">
+      <c r="C190" s="3">
         <v>17</v>
       </c>
-      <c r="D190" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E190" s="13" t="s">
+      <c r="D190" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E190" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F190" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="G190" s="15">
+      <c r="G190" s="12">
         <v>1248000</v>
       </c>
-      <c r="H190" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I190" s="40"/>
-    </row>
-    <row r="191" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A191" s="30">
+      <c r="H190" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I190" s="33"/>
+    </row>
+    <row r="191" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A191" s="25">
         <v>20</v>
       </c>
       <c r="B191" s="3">
         <v>458</v>
       </c>
-      <c r="C191" s="18">
+      <c r="C191" s="3">
         <v>18</v>
       </c>
-      <c r="D191" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E191" s="13" t="s">
+      <c r="D191" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E191" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F191" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="G191" s="15">
+      <c r="G191" s="12">
         <v>1450000</v>
       </c>
-      <c r="H191" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I191" s="40"/>
-    </row>
-    <row r="192" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="30">
+      <c r="H191" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I191" s="33"/>
+    </row>
+    <row r="192" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="25">
         <v>6</v>
       </c>
       <c r="B192" s="3">
         <v>454</v>
       </c>
-      <c r="C192" s="18">
+      <c r="C192" s="3">
         <v>19</v>
       </c>
-      <c r="D192" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E192" s="13" t="s">
+      <c r="D192" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E192" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F192" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G192" s="15">
+      <c r="G192" s="12">
         <v>1522500</v>
       </c>
-      <c r="H192" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I192" s="40"/>
-    </row>
-    <row r="193" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="30">
+      <c r="H192" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I192" s="33"/>
+    </row>
+    <row r="193" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A193" s="25">
         <v>14</v>
       </c>
       <c r="B193" s="3">
         <v>362</v>
       </c>
-      <c r="C193" s="18">
+      <c r="C193" s="3">
         <v>20</v>
       </c>
-      <c r="D193" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E193" s="13" t="s">
+      <c r="D193" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E193" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F193" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="G193" s="15">
+      <c r="G193" s="12">
         <v>2000000</v>
       </c>
-      <c r="H193" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I193" s="40"/>
-    </row>
-    <row r="194" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A194" s="30">
+      <c r="H193" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I193" s="33"/>
+    </row>
+    <row r="194" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A194" s="25">
         <v>2</v>
       </c>
       <c r="B194" s="3">
         <v>355</v>
       </c>
-      <c r="C194" s="18">
+      <c r="C194" s="3">
         <v>21</v>
       </c>
-      <c r="D194" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E194" s="13" t="s">
+      <c r="D194" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E194" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F194" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="G194" s="15">
+      <c r="G194" s="12">
         <v>784000</v>
       </c>
-      <c r="H194" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I194" s="40"/>
-    </row>
-    <row r="195" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="30">
+      <c r="H194" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I194" s="33"/>
+    </row>
+    <row r="195" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="25">
         <v>15</v>
       </c>
       <c r="B195" s="3">
         <v>279</v>
       </c>
-      <c r="C195" s="18">
+      <c r="C195" s="3">
         <v>22</v>
       </c>
-      <c r="D195" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E195" s="13" t="s">
+      <c r="D195" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E195" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="G195" s="15">
+      <c r="G195" s="12">
         <v>2400000</v>
       </c>
-      <c r="H195" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I195" s="40"/>
-    </row>
-    <row r="196" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A196" s="30">
+      <c r="H195" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I195" s="33"/>
+    </row>
+    <row r="196" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A196" s="25">
         <v>3</v>
       </c>
       <c r="B196" s="3">
         <v>202</v>
       </c>
-      <c r="C196" s="18">
+      <c r="C196" s="3">
         <v>23</v>
       </c>
-      <c r="D196" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E196" s="13" t="s">
+      <c r="D196" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E196" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F196" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="G196" s="15">
+      <c r="G196" s="12">
         <v>343000</v>
       </c>
-      <c r="H196" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I196" s="40"/>
-    </row>
-    <row r="197" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="28">
+      <c r="H196" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I196" s="33"/>
+    </row>
+    <row r="197" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="23">
         <v>24</v>
       </c>
-      <c r="B197" s="10">
+      <c r="B197" s="8">
         <v>159</v>
       </c>
-      <c r="C197" s="10">
+      <c r="C197" s="8">
         <v>24</v>
       </c>
-      <c r="D197" s="10" t="s">
+      <c r="D197" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E197" s="11" t="s">
+      <c r="E197" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="F197" s="12" t="s">
+      <c r="F197" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="G197" s="14">
+      <c r="G197" s="11">
         <v>43400</v>
       </c>
-      <c r="H197" s="12" t="s">
+      <c r="H197" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I197" s="40"/>
-    </row>
-    <row r="198" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A198" s="30">
+      <c r="I197" s="33"/>
+    </row>
+    <row r="198" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A198" s="25">
         <v>18</v>
       </c>
       <c r="B198" s="3">
         <v>139</v>
       </c>
-      <c r="C198" s="18">
+      <c r="C198" s="3">
         <v>25</v>
       </c>
-      <c r="D198" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E198" s="13" t="s">
+      <c r="D198" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E198" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F198" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="G198" s="15">
+      <c r="G198" s="12">
         <v>504000</v>
       </c>
-      <c r="H198" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I198" s="40"/>
-    </row>
-    <row r="199" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A199" s="30">
+      <c r="H198" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I198" s="33"/>
+    </row>
+    <row r="199" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A199" s="25">
         <v>28</v>
       </c>
       <c r="B199" s="3">
         <v>134</v>
       </c>
-      <c r="C199" s="18">
+      <c r="C199" s="3">
         <v>26</v>
       </c>
-      <c r="D199" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E199" s="13" t="s">
+      <c r="D199" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E199" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F199" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="G199" s="15">
+      <c r="G199" s="12">
         <v>2671200</v>
       </c>
-      <c r="H199" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I199" s="40"/>
-    </row>
-    <row r="200" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="30">
+      <c r="H199" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I199" s="33"/>
+    </row>
+    <row r="200" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="25">
         <v>25</v>
       </c>
       <c r="B200" s="3">
         <v>77</v>
       </c>
-      <c r="C200" s="18">
+      <c r="C200" s="3">
         <v>27</v>
       </c>
-      <c r="D200" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="E200" s="13" t="s">
+      <c r="D200" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E200" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F200" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="G200" s="15">
+      <c r="G200" s="12">
         <v>385000</v>
       </c>
-      <c r="H200" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I200" s="40"/>
-    </row>
-    <row r="201" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="32">
+      <c r="H200" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I200" s="33"/>
+    </row>
+    <row r="201" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A201" s="26">
         <v>26</v>
       </c>
-      <c r="B201" s="33">
+      <c r="B201" s="27">
         <v>62</v>
       </c>
-      <c r="C201" s="43">
+      <c r="C201" s="27">
         <v>28</v>
       </c>
-      <c r="D201" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="E201" s="44" t="s">
+      <c r="D201" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="E201" s="28" t="s">
         <v>206</v>
       </c>
-      <c r="F201" s="35" t="s">
+      <c r="F201" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="G201" s="36">
+      <c r="G201" s="30">
         <v>100000</v>
       </c>
-      <c r="H201" s="47" t="s">
-        <v>200</v>
-      </c>
-      <c r="I201" s="45">
+      <c r="H201" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="I201" s="36">
         <f>SUM(G197,G185,G178,G177,G176,G175,G174)</f>
         <v>14321861</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="22">
+    <row r="202" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A202" s="17">
         <v>12</v>
       </c>
-      <c r="B202" s="23">
+      <c r="B202" s="18">
         <v>992</v>
       </c>
-      <c r="C202" s="23">
+      <c r="C202" s="18">
         <v>1</v>
       </c>
-      <c r="D202" s="23" t="s">
+      <c r="D202" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="E202" s="24" t="s">
+      <c r="E202" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="F202" s="25" t="s">
+      <c r="F202" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="G202" s="26">
+      <c r="G202" s="21">
         <v>1850000</v>
       </c>
-      <c r="H202" s="25" t="s">
+      <c r="H202" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="I202" s="39"/>
-    </row>
-    <row r="203" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="28">
+      <c r="I202" s="31"/>
+    </row>
+    <row r="203" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A203" s="23">
         <v>4</v>
       </c>
-      <c r="B203" s="10">
+      <c r="B203" s="8">
         <v>267</v>
       </c>
-      <c r="C203" s="10">
+      <c r="C203" s="8">
         <v>2</v>
       </c>
-      <c r="D203" s="10" t="s">
+      <c r="D203" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E203" s="11" t="s">
+      <c r="E203" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="F203" s="12" t="s">
+      <c r="F203" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="G203" s="14">
+      <c r="G203" s="11">
         <v>985000</v>
       </c>
-      <c r="H203" s="12" t="s">
+      <c r="H203" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I203" s="40"/>
-    </row>
-    <row r="204" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="28">
+      <c r="I203" s="33"/>
+    </row>
+    <row r="204" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A204" s="23">
         <v>7</v>
       </c>
-      <c r="B204" s="10">
+      <c r="B204" s="8">
         <v>225</v>
       </c>
-      <c r="C204" s="10">
+      <c r="C204" s="8">
         <v>3</v>
       </c>
-      <c r="D204" s="10" t="s">
+      <c r="D204" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E204" s="11" t="s">
+      <c r="E204" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="F204" s="12" t="s">
+      <c r="F204" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="G204" s="14">
+      <c r="G204" s="11">
         <v>2000000</v>
       </c>
-      <c r="H204" s="12" t="s">
+      <c r="H204" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I204" s="40"/>
-    </row>
-    <row r="205" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="28">
+      <c r="I204" s="33"/>
+    </row>
+    <row r="205" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A205" s="23">
         <v>13</v>
       </c>
-      <c r="B205" s="10">
+      <c r="B205" s="8">
         <v>212</v>
       </c>
-      <c r="C205" s="10">
+      <c r="C205" s="8">
         <v>4</v>
       </c>
-      <c r="D205" s="10" t="s">
+      <c r="D205" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E205" s="11" t="s">
+      <c r="E205" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="F205" s="12" t="s">
+      <c r="F205" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="G205" s="14">
+      <c r="G205" s="11">
         <v>3000000</v>
       </c>
-      <c r="H205" s="12" t="s">
+      <c r="H205" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I205" s="40"/>
-    </row>
-    <row r="206" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A206" s="28">
+      <c r="I205" s="33"/>
+    </row>
+    <row r="206" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A206" s="23">
         <v>1</v>
       </c>
-      <c r="B206" s="10">
+      <c r="B206" s="8">
         <v>146</v>
       </c>
-      <c r="C206" s="10">
+      <c r="C206" s="8">
         <v>5</v>
       </c>
-      <c r="D206" s="10" t="s">
+      <c r="D206" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E206" s="11" t="s">
+      <c r="E206" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="F206" s="12" t="s">
+      <c r="F206" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="G206" s="14">
+      <c r="G206" s="11">
         <v>689000</v>
       </c>
-      <c r="H206" s="12" t="s">
+      <c r="H206" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I206" s="40"/>
-    </row>
-    <row r="207" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A207" s="30">
+      <c r="I206" s="33"/>
+    </row>
+    <row r="207" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A207" s="25">
         <v>3</v>
       </c>
       <c r="B207" s="3">
@@ -7009,43 +6992,43 @@
       <c r="F207" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="G207" s="20">
+      <c r="G207" s="15">
         <v>3000000</v>
       </c>
-      <c r="H207" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I207" s="40"/>
-    </row>
-    <row r="208" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="28">
+      <c r="H207" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I207" s="33"/>
+    </row>
+    <row r="208" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A208" s="23">
         <v>6</v>
       </c>
-      <c r="B208" s="10">
+      <c r="B208" s="8">
         <v>111</v>
       </c>
-      <c r="C208" s="10">
+      <c r="C208" s="8">
         <v>7</v>
       </c>
-      <c r="D208" s="10" t="s">
+      <c r="D208" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E208" s="11" t="s">
+      <c r="E208" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="F208" s="12" t="s">
+      <c r="F208" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="G208" s="14">
+      <c r="G208" s="11">
         <v>600000</v>
       </c>
-      <c r="H208" s="12" t="s">
+      <c r="H208" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I208" s="40"/>
-    </row>
-    <row r="209" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A209" s="30">
+      <c r="I208" s="33"/>
+    </row>
+    <row r="209" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A209" s="25">
         <v>8</v>
       </c>
       <c r="B209" s="3">
@@ -7063,16 +7046,16 @@
       <c r="F209" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="G209" s="15">
+      <c r="G209" s="12">
         <v>2000000</v>
       </c>
-      <c r="H209" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I209" s="40"/>
-    </row>
-    <row r="210" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="30">
+      <c r="H209" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I209" s="33"/>
+    </row>
+    <row r="210" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="25">
         <v>11</v>
       </c>
       <c r="B210" s="3">
@@ -7090,16 +7073,16 @@
       <c r="F210" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="G210" s="15">
+      <c r="G210" s="12">
         <v>3000000</v>
       </c>
-      <c r="H210" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I210" s="40"/>
-    </row>
-    <row r="211" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A211" s="30">
+      <c r="H210" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I210" s="33"/>
+    </row>
+    <row r="211" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A211" s="25">
         <v>10</v>
       </c>
       <c r="B211" s="3">
@@ -7117,43 +7100,43 @@
       <c r="F211" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="G211" s="15">
+      <c r="G211" s="12">
         <v>2966700</v>
       </c>
-      <c r="H211" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I211" s="40"/>
-    </row>
-    <row r="212" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A212" s="28">
+      <c r="H211" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I211" s="33"/>
+    </row>
+    <row r="212" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A212" s="23">
         <v>5</v>
       </c>
-      <c r="B212" s="10">
+      <c r="B212" s="8">
         <v>57</v>
       </c>
-      <c r="C212" s="10">
+      <c r="C212" s="8">
         <v>11</v>
       </c>
-      <c r="D212" s="10" t="s">
+      <c r="D212" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E212" s="11" t="s">
+      <c r="E212" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="F212" s="12" t="s">
+      <c r="F212" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G212" s="14">
+      <c r="G212" s="11">
         <v>180000</v>
       </c>
-      <c r="H212" s="12" t="s">
+      <c r="H212" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I212" s="40"/>
-    </row>
-    <row r="213" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A213" s="30">
+      <c r="I212" s="33"/>
+    </row>
+    <row r="213" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A213" s="25">
         <v>2</v>
       </c>
       <c r="B213" s="3">
@@ -7171,40 +7154,40 @@
       <c r="F213" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G213" s="15">
+      <c r="G213" s="12">
         <v>1522500</v>
       </c>
-      <c r="H213" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I213" s="40"/>
-    </row>
-    <row r="214" spans="1:9" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="48">
+      <c r="H213" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I213" s="33"/>
+    </row>
+    <row r="214" spans="1:9" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A214" s="37">
         <v>9</v>
       </c>
-      <c r="B214" s="49">
+      <c r="B214" s="38">
         <v>48</v>
       </c>
-      <c r="C214" s="49">
+      <c r="C214" s="38">
         <v>13</v>
       </c>
-      <c r="D214" s="49" t="s">
+      <c r="D214" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="E214" s="50" t="s">
+      <c r="E214" s="39" t="s">
         <v>207</v>
       </c>
-      <c r="F214" s="51" t="s">
+      <c r="F214" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="G214" s="52">
+      <c r="G214" s="41">
         <v>80000</v>
       </c>
-      <c r="H214" s="51" t="s">
+      <c r="H214" s="40" t="s">
         <v>210</v>
       </c>
-      <c r="I214" s="45">
+      <c r="I214" s="36">
         <f>SUM(G214,G212,G208,G206,G205,G204,G203,G202)</f>
         <v>9384000</v>
       </c>
